--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,42 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Chile)</t>
+  </si>
+  <si>
+    <t>2026-08-10 01:43:53</t>
   </si>
 </sst>
 </file>
@@ -585,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +864,732 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2">
+        <v>2.42</v>
+      </c>
+      <c r="G2">
+        <v>2.6</v>
+      </c>
+      <c r="H2">
+        <v>3.45</v>
+      </c>
+      <c r="I2">
+        <v>3.9</v>
+      </c>
+      <c r="J2">
+        <v>2.92</v>
+      </c>
+      <c r="K2">
+        <v>3.1</v>
+      </c>
+      <c r="L2">
+        <v>1.56</v>
+      </c>
+      <c r="M2">
+        <v>1.16</v>
+      </c>
+      <c r="N2">
+        <v>2.26</v>
+      </c>
+      <c r="O2">
+        <v>1.68</v>
+      </c>
+      <c r="P2">
+        <v>1.42</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>1.14</v>
+      </c>
+      <c r="S2">
+        <v>6.8</v>
+      </c>
+      <c r="T2">
+        <v>2.32</v>
+      </c>
+      <c r="U2">
+        <v>1.62</v>
+      </c>
+      <c r="V2">
+        <v>1.34</v>
+      </c>
+      <c r="W2">
+        <v>1.62</v>
+      </c>
+      <c r="X2">
+        <v>7.6</v>
+      </c>
+      <c r="Y2">
+        <v>9</v>
+      </c>
+      <c r="Z2">
+        <v>25</v>
+      </c>
+      <c r="AA2">
+        <v>110</v>
+      </c>
+      <c r="AB2">
+        <v>6.8</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2">
+        <v>80</v>
+      </c>
+      <c r="AF2">
+        <v>14.5</v>
+      </c>
+      <c r="AG2">
+        <v>13.5</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>130</v>
+      </c>
+      <c r="AJ2">
+        <v>42</v>
+      </c>
+      <c r="AK2">
+        <v>44</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>340</v>
+      </c>
+      <c r="AN2">
+        <v>65</v>
+      </c>
+      <c r="AO2">
+        <v>140</v>
+      </c>
+      <c r="AP2">
+        <v>6.6</v>
+      </c>
+      <c r="AQ2">
+        <v>7.6</v>
+      </c>
+      <c r="AR2">
+        <v>20</v>
+      </c>
+      <c r="AS2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>5.7</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>15</v>
+      </c>
+      <c r="AW2">
+        <v>8.4</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2">
+        <v>24</v>
+      </c>
+      <c r="BA2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>26</v>
+      </c>
+      <c r="BC2">
+        <v>7.8</v>
+      </c>
+      <c r="BD2">
+        <v>8.6</v>
+      </c>
+      <c r="BE2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF2">
+        <v>42</v>
+      </c>
+      <c r="BG2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH2">
+        <v>2.52</v>
+      </c>
+      <c r="BI2">
+        <v>2.06</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2">
+        <v>9.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>11</v>
+      </c>
+      <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>4.4</v>
+      </c>
+      <c r="BP2">
+        <v>26</v>
+      </c>
+      <c r="BQ2">
+        <v>8</v>
+      </c>
+      <c r="BR2">
+        <v>60</v>
+      </c>
+      <c r="BS2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT2">
+        <v>7</v>
+      </c>
+      <c r="BU2">
+        <v>5</v>
+      </c>
+      <c r="BV2">
+        <v>42</v>
+      </c>
+      <c r="BW2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>10</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>10</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.07</v>
+      </c>
+      <c r="Q3">
+        <v>1.01</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.24</v>
+      </c>
+      <c r="Q4">
+        <v>1.01</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 01:43:53</t>
+    <t>2026-08-10 03:53:36</t>
   </si>
 </sst>
 </file>
@@ -883,37 +883,37 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
         <v>2.6</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
         <v>2.26</v>
       </c>
       <c r="O2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -922,7 +922,7 @@
         <v>1.14</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T2">
         <v>2.32</v>
@@ -931,7 +931,7 @@
         <v>1.62</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
         <v>1.62</v>
@@ -940,13 +940,13 @@
         <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>6.8</v>
@@ -955,10 +955,10 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
@@ -979,16 +979,16 @@
         <v>44</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AM2">
         <v>340</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP2">
         <v>6.6</v>
@@ -1000,7 +1000,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
         <v>5.7</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1024,28 +1024,28 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB2">
         <v>26</v>
       </c>
       <c r="BC2">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>42</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI2">
         <v>2.06</v>
@@ -1060,28 +1060,28 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
         <v>5</v>
@@ -1090,7 +1090,7 @@
         <v>42</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 03:53:36</t>
+    <t>2026-08-10 06:03:16</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,7 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
         <v>2.6</v>
@@ -895,25 +895,25 @@
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
         <v>1.69</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -997,7 +997,7 @@
         <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS2">
         <v>9.800000000000001</v>
@@ -1009,10 +1009,10 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1033,7 +1033,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2">
         <v>10.5</v>
@@ -1045,22 +1045,22 @@
         <v>10</v>
       </c>
       <c r="BH2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>5.4</v>
@@ -1069,28 +1069,28 @@
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX2">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 06:03:16</t>
+    <t>2026-08-10 08:12:44</t>
   </si>
 </sst>
 </file>
@@ -883,37 +883,37 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -922,187 +922,187 @@
         <v>1.14</v>
       </c>
       <c r="S2">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>91</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 08:12:44</t>
+    <t>2026-08-10 10:22:49</t>
   </si>
 </sst>
 </file>
@@ -883,19 +883,19 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
         <v>1000</v>
       </c>
       <c r="H2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I2">
         <v>1000</v>
       </c>
       <c r="J2">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K2">
         <v>6.2</v>
@@ -910,7 +910,7 @@
         <v>1.4</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
         <v>1.25</v>
@@ -934,10 +934,10 @@
         <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
         <v>1000</v>
@@ -994,115 +994,115 @@
         <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>91</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>2026-08-12</t>
   </si>
   <si>
@@ -271,6 +274,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>00:45:00</t>
+  </si>
+  <si>
     <t>Talleres</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -289,7 +298,10 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 10:22:49</t>
+    <t>Union Magdalena</t>
+  </si>
+  <si>
+    <t>2026-08-10 12:32:55</t>
   </si>
 </sst>
 </file>
@@ -621,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -871,241 +883,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>2.36</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2">
-        <v>1.13</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>1.13</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>1.13</v>
+        <v>34</v>
       </c>
       <c r="AT2">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>1.13</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>1.13</v>
+        <v>46</v>
       </c>
       <c r="AX2">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>1.13</v>
+        <v>25</v>
       </c>
       <c r="BA2">
-        <v>1.13</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>1.13</v>
+        <v>29</v>
       </c>
       <c r="BC2">
-        <v>1.13</v>
+        <v>28</v>
       </c>
       <c r="BD2">
-        <v>1.13</v>
+        <v>55</v>
       </c>
       <c r="BE2">
-        <v>1.13</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>1.13</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>1.13</v>
+        <v>38</v>
       </c>
       <c r="BH2">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1113,16 +1125,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1347,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1355,16 +1367,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1589,7 +1601,249 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>3.25</v>
+      </c>
+      <c r="G5">
+        <v>4.5</v>
+      </c>
+      <c r="H5">
+        <v>2.16</v>
+      </c>
+      <c r="I5">
+        <v>2.44</v>
+      </c>
+      <c r="J5">
+        <v>2.92</v>
+      </c>
+      <c r="K5">
+        <v>3.75</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.1</v>
+      </c>
+      <c r="N5">
+        <v>2.42</v>
+      </c>
+      <c r="O5">
+        <v>1.52</v>
+      </c>
+      <c r="P5">
+        <v>1.53</v>
+      </c>
+      <c r="Q5">
+        <v>2.54</v>
+      </c>
+      <c r="R5">
+        <v>1.15</v>
+      </c>
+      <c r="S5">
+        <v>3.95</v>
+      </c>
+      <c r="T5">
+        <v>1.94</v>
+      </c>
+      <c r="U5">
+        <v>1.62</v>
+      </c>
+      <c r="V5">
+        <v>1.69</v>
+      </c>
+      <c r="W5">
+        <v>1.28</v>
+      </c>
+      <c r="X5">
+        <v>10.5</v>
+      </c>
+      <c r="Y5">
+        <v>8.6</v>
+      </c>
+      <c r="Z5">
+        <v>15.5</v>
+      </c>
+      <c r="AA5">
+        <v>40</v>
+      </c>
+      <c r="AB5">
+        <v>13</v>
+      </c>
+      <c r="AC5">
+        <v>8.6</v>
+      </c>
+      <c r="AD5">
+        <v>14.5</v>
+      </c>
+      <c r="AE5">
+        <v>40</v>
+      </c>
+      <c r="AF5">
+        <v>34</v>
+      </c>
+      <c r="AG5">
+        <v>22</v>
+      </c>
+      <c r="AH5">
+        <v>29</v>
+      </c>
+      <c r="AI5">
+        <v>75</v>
+      </c>
+      <c r="AJ5">
+        <v>130</v>
+      </c>
+      <c r="AK5">
+        <v>85</v>
+      </c>
+      <c r="AL5">
+        <v>120</v>
+      </c>
+      <c r="AM5">
+        <v>240</v>
+      </c>
+      <c r="AN5">
+        <v>130</v>
+      </c>
+      <c r="AO5">
+        <v>42</v>
+      </c>
+      <c r="AP5">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5">
+        <v>5.3</v>
+      </c>
+      <c r="AR5">
+        <v>9.4</v>
+      </c>
+      <c r="AS5">
+        <v>23</v>
+      </c>
+      <c r="AT5">
+        <v>8</v>
+      </c>
+      <c r="AU5">
+        <v>5.4</v>
+      </c>
+      <c r="AV5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW5">
+        <v>23</v>
+      </c>
+      <c r="AX5">
+        <v>20</v>
+      </c>
+      <c r="AY5">
+        <v>13</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>24</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>2026-08-12</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>00:45:00</t>
   </si>
   <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
     <t>Talleres</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>Boca Juniors de Cali</t>
   </si>
   <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -301,7 +310,10 @@
     <t>Union Magdalena</t>
   </si>
   <si>
-    <t>2026-08-10 12:32:55</t>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
+    <t>2026-08-10 14:41:40</t>
   </si>
 </sst>
 </file>
@@ -633,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -883,49 +895,49 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F2">
         <v>2.46</v>
       </c>
       <c r="G2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
         <v>3.9</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
         <v>3.1</v>
@@ -934,25 +946,25 @@
         <v>1.15</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T2">
         <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V2">
         <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z2">
         <v>24</v>
@@ -961,7 +973,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC2">
         <v>7.4</v>
@@ -970,7 +982,7 @@
         <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
         <v>13.5</v>
@@ -994,7 +1006,7 @@
         <v>90</v>
       </c>
       <c r="AM2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN2">
         <v>55</v>
@@ -1015,16 +1027,16 @@
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1036,13 +1048,13 @@
         <v>25</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB2">
         <v>29</v>
       </c>
       <c r="BC2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD2">
         <v>55</v>
@@ -1054,70 +1066,70 @@
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="CB2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1125,16 +1137,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1359,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1367,16 +1379,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1601,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1609,241 +1621,483 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H5">
+        <v>1.95</v>
+      </c>
+      <c r="I5">
+        <v>2.12</v>
+      </c>
+      <c r="J5">
+        <v>2.96</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>1.47</v>
+      </c>
+      <c r="M5">
+        <v>1.12</v>
+      </c>
+      <c r="N5">
+        <v>2.44</v>
+      </c>
+      <c r="O5">
+        <v>1.44</v>
+      </c>
+      <c r="P5">
+        <v>1.54</v>
+      </c>
+      <c r="Q5">
+        <v>2.44</v>
+      </c>
+      <c r="R5">
+        <v>1.19</v>
+      </c>
+      <c r="S5">
+        <v>1.05</v>
+      </c>
+      <c r="T5">
         <v>2.16</v>
       </c>
-      <c r="I5">
-        <v>2.44</v>
-      </c>
-      <c r="J5">
-        <v>2.92</v>
-      </c>
-      <c r="K5">
-        <v>3.75</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.1</v>
-      </c>
-      <c r="N5">
-        <v>2.42</v>
-      </c>
-      <c r="O5">
-        <v>1.52</v>
-      </c>
-      <c r="P5">
-        <v>1.53</v>
-      </c>
-      <c r="Q5">
-        <v>2.54</v>
-      </c>
-      <c r="R5">
-        <v>1.15</v>
-      </c>
-      <c r="S5">
-        <v>3.95</v>
-      </c>
-      <c r="T5">
-        <v>1.94</v>
-      </c>
       <c r="U5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V5">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="W5">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AG5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI5">
         <v>75</v>
       </c>
       <c r="AJ5">
+        <v>170</v>
+      </c>
+      <c r="AK5">
+        <v>110</v>
+      </c>
+      <c r="AL5">
         <v>130</v>
       </c>
-      <c r="AK5">
-        <v>85</v>
-      </c>
-      <c r="AL5">
-        <v>120</v>
-      </c>
       <c r="AM5">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN5">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AO5">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AP5">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="AQ5">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="AR5">
+        <v>3.25</v>
+      </c>
+      <c r="AS5">
+        <v>3.8</v>
+      </c>
+      <c r="AT5">
+        <v>3.35</v>
+      </c>
+      <c r="AU5">
+        <v>2.92</v>
+      </c>
+      <c r="AV5">
+        <v>3.3</v>
+      </c>
+      <c r="AW5">
+        <v>3.85</v>
+      </c>
+      <c r="AX5">
+        <v>3.9</v>
+      </c>
+      <c r="AY5">
+        <v>3.65</v>
+      </c>
+      <c r="AZ5">
+        <v>3.8</v>
+      </c>
+      <c r="BA5">
+        <v>4</v>
+      </c>
+      <c r="BB5">
+        <v>4.2</v>
+      </c>
+      <c r="BC5">
+        <v>4.1</v>
+      </c>
+      <c r="BD5">
+        <v>4.1</v>
+      </c>
+      <c r="BE5">
+        <v>4.2</v>
+      </c>
+      <c r="BF5">
+        <v>4.2</v>
+      </c>
+      <c r="BG5">
+        <v>3.8</v>
+      </c>
+      <c r="BH5">
+        <v>3.15</v>
+      </c>
+      <c r="BI5">
+        <v>2.24</v>
+      </c>
+      <c r="BJ5">
+        <v>14</v>
+      </c>
+      <c r="BK5">
+        <v>3.75</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>5</v>
+      </c>
+      <c r="BN5">
         <v>9.4</v>
       </c>
-      <c r="AS5">
-        <v>23</v>
-      </c>
-      <c r="AT5">
-        <v>8</v>
-      </c>
-      <c r="AU5">
+      <c r="BO5">
+        <v>3.3</v>
+      </c>
+      <c r="BP5">
+        <v>65</v>
+      </c>
+      <c r="BQ5">
+        <v>4.7</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>4.8</v>
+      </c>
+      <c r="BT5">
+        <v>5.2</v>
+      </c>
+      <c r="BU5">
+        <v>2.58</v>
+      </c>
+      <c r="BV5">
+        <v>20</v>
+      </c>
+      <c r="BW5">
+        <v>4.1</v>
+      </c>
+      <c r="BX5">
+        <v>50</v>
+      </c>
+      <c r="BY5">
+        <v>4.6</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6">
+        <v>1.35</v>
+      </c>
+      <c r="G6">
+        <v>1.37</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>12.5</v>
+      </c>
+      <c r="J6">
         <v>5.4</v>
       </c>
-      <c r="AV5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW5">
-        <v>23</v>
-      </c>
-      <c r="AX5">
-        <v>20</v>
-      </c>
-      <c r="AY5">
-        <v>13</v>
-      </c>
-      <c r="AZ5">
-        <v>17</v>
-      </c>
-      <c r="BA5">
+      <c r="K6">
+        <v>5.9</v>
+      </c>
+      <c r="L6">
+        <v>1.36</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>4.5</v>
+      </c>
+      <c r="O6">
+        <v>1.26</v>
+      </c>
+      <c r="P6">
+        <v>2.18</v>
+      </c>
+      <c r="Q6">
+        <v>1.8</v>
+      </c>
+      <c r="R6">
+        <v>1.45</v>
+      </c>
+      <c r="S6">
+        <v>3.05</v>
+      </c>
+      <c r="T6">
+        <v>2.06</v>
+      </c>
+      <c r="U6">
+        <v>1.76</v>
+      </c>
+      <c r="V6">
+        <v>1.09</v>
+      </c>
+      <c r="W6">
+        <v>3.7</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
         <v>1.01</v>
       </c>
-      <c r="BB5">
+      <c r="AQ6">
         <v>1.01</v>
       </c>
-      <c r="BC5">
+      <c r="AR6">
         <v>1.01</v>
       </c>
-      <c r="BD5">
+      <c r="AS6">
         <v>1.01</v>
       </c>
-      <c r="BE5">
+      <c r="AT6">
         <v>1.01</v>
       </c>
-      <c r="BF5">
+      <c r="AU6">
         <v>1.01</v>
       </c>
-      <c r="BG5">
-        <v>24</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
+      <c r="AV6">
         <v>1.01</v>
       </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
+      <c r="AW6">
         <v>1.01</v>
       </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
+      <c r="AX6">
         <v>1.01</v>
       </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
+      <c r="AY6">
         <v>1.01</v>
       </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
+      <c r="AZ6">
         <v>1.01</v>
       </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
+      <c r="BA6">
         <v>1.01</v>
       </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
+      <c r="BB6">
         <v>1.01</v>
       </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
+      <c r="BC6">
         <v>1.01</v>
       </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
+      <c r="BD6">
         <v>1.01</v>
       </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>95</v>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.04</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.04</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.04</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.04</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.04</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.04</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.04</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.04</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.04</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.04</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -313,7 +313,7 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
-    <t>2026-08-10 14:41:40</t>
+    <t>2026-08-10 16:49:46</t>
   </si>
 </sst>
 </file>
@@ -928,10 +928,10 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>1.7</v>
@@ -946,7 +946,7 @@
         <v>1.15</v>
       </c>
       <c r="S2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T2">
         <v>2.42</v>
@@ -1027,7 +1027,7 @@
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1633,22 +1633,22 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G5">
         <v>5.5</v>
       </c>
       <c r="H5">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J5">
         <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
         <v>1.47</v>
@@ -1657,22 +1657,22 @@
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="O5">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="P5">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="T5">
         <v>2.16</v>
@@ -1681,34 +1681,34 @@
         <v>1.61</v>
       </c>
       <c r="V5">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="W5">
         <v>1.22</v>
       </c>
       <c r="X5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA5">
         <v>32</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>9</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF5">
         <v>44</v>
@@ -1717,7 +1717,7 @@
         <v>25</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI5">
         <v>75</v>
@@ -1735,70 +1735,70 @@
         <v>250</v>
       </c>
       <c r="AN5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO5">
         <v>32</v>
       </c>
       <c r="AP5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ5">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AR5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AS5">
+        <v>3.95</v>
+      </c>
+      <c r="AT5">
+        <v>3.45</v>
+      </c>
+      <c r="AU5">
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <v>3.35</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>4.1</v>
+      </c>
+      <c r="AY5">
         <v>3.8</v>
       </c>
-      <c r="AT5">
-        <v>3.35</v>
-      </c>
-      <c r="AU5">
-        <v>2.92</v>
-      </c>
-      <c r="AV5">
-        <v>3.3</v>
-      </c>
-      <c r="AW5">
-        <v>3.85</v>
-      </c>
-      <c r="AX5">
+      <c r="AZ5">
         <v>3.9</v>
       </c>
-      <c r="AY5">
-        <v>3.65</v>
-      </c>
-      <c r="AZ5">
-        <v>3.8</v>
-      </c>
       <c r="BA5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5">
         <v>14</v>
@@ -1816,10 +1816,10 @@
         <v>9.4</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BQ5">
         <v>4.7</v>
@@ -1831,19 +1831,19 @@
         <v>4.8</v>
       </c>
       <c r="BT5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU5">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="BV5">
         <v>20</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY5">
         <v>4.6</v>
@@ -1875,7 +1875,7 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G6">
         <v>1.37</v>
@@ -1884,46 +1884,46 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
         <v>3.7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>League</t>
   </si>
@@ -262,12 +262,6 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
-    <t>Colombian Primera B</t>
-  </si>
-  <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
     <t>2026-08-12</t>
   </si>
   <si>
@@ -277,12 +271,6 @@
     <t>00:30:00</t>
   </si>
   <si>
-    <t>00:45:00</t>
-  </si>
-  <si>
-    <t>01:05:00</t>
-  </si>
-  <si>
     <t>Talleres</t>
   </si>
   <si>
@@ -292,12 +280,6 @@
     <t>Estudiantes</t>
   </si>
   <si>
-    <t>Boca Juniors de Cali</t>
-  </si>
-  <si>
-    <t>Junior FC Barranquilla</t>
-  </si>
-  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -307,13 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>Union Magdalena</t>
-  </si>
-  <si>
-    <t>Deportivo Pereira</t>
-  </si>
-  <si>
-    <t>2026-08-10 16:49:46</t>
+    <t>2026-08-10 18:57:53</t>
   </si>
 </sst>
 </file>
@@ -645,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -895,34 +871,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>2.46</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -931,19 +907,19 @@
         <v>1.17</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
         <v>1.7</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q2">
         <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S2">
         <v>7.2</v>
@@ -1015,7 +991,7 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2">
         <v>7.8</v>
@@ -1072,19 +1048,19 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BJ2">
         <v>18</v>
       </c>
       <c r="BK2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BN2">
         <v>7</v>
@@ -1096,16 +1072,16 @@
         <v>34</v>
       </c>
       <c r="BQ2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU2">
         <v>4.4</v>
@@ -1114,7 +1090,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1129,7 +1105,7 @@
         <v>1.59</v>
       </c>
       <c r="CB2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1137,241 +1113,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>86</v>
       </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.07</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
+        <v>2.34</v>
+      </c>
+      <c r="R3">
+        <v>1.26</v>
+      </c>
+      <c r="S3">
+        <v>4.3</v>
+      </c>
+      <c r="T3">
+        <v>1.9</v>
+      </c>
+      <c r="U3">
+        <v>1.92</v>
+      </c>
+      <c r="V3">
+        <v>1.53</v>
+      </c>
+      <c r="W3">
+        <v>1.45</v>
+      </c>
+      <c r="X3">
+        <v>11</v>
+      </c>
+      <c r="Y3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z3">
+        <v>18</v>
+      </c>
+      <c r="AA3">
+        <v>46</v>
+      </c>
+      <c r="AB3">
+        <v>10.5</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>13.5</v>
+      </c>
+      <c r="AE3">
+        <v>38</v>
+      </c>
+      <c r="AF3">
+        <v>21</v>
+      </c>
+      <c r="AG3">
+        <v>14</v>
+      </c>
+      <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>55</v>
+      </c>
+      <c r="AJ3">
+        <v>70</v>
+      </c>
+      <c r="AK3">
+        <v>42</v>
+      </c>
+      <c r="AL3">
+        <v>60</v>
+      </c>
+      <c r="AM3">
+        <v>150</v>
+      </c>
+      <c r="AN3">
+        <v>46</v>
+      </c>
+      <c r="AO3">
+        <v>38</v>
+      </c>
+      <c r="AP3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR3">
+        <v>14.5</v>
+      </c>
+      <c r="AS3">
+        <v>7.6</v>
+      </c>
+      <c r="AT3">
+        <v>8.6</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>10.5</v>
+      </c>
+      <c r="AW3">
+        <v>7.2</v>
+      </c>
+      <c r="AX3">
+        <v>16.5</v>
+      </c>
+      <c r="AY3">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>7.8</v>
+      </c>
+      <c r="BB3">
+        <v>7.8</v>
+      </c>
+      <c r="BC3">
+        <v>32</v>
+      </c>
+      <c r="BD3">
+        <v>7.8</v>
+      </c>
+      <c r="BE3">
+        <v>8.6</v>
+      </c>
+      <c r="BF3">
+        <v>32</v>
+      </c>
+      <c r="BG3">
+        <v>7.2</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
         <v>1.01</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3">
-        <v>0</v>
-      </c>
-      <c r="BE3">
-        <v>0</v>
-      </c>
-      <c r="BF3">
-        <v>0</v>
-      </c>
-      <c r="BG3">
-        <v>0</v>
-      </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3">
-        <v>0</v>
-      </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1379,725 +1355,241 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>1.62</v>
+      </c>
+      <c r="G4">
+        <v>1.72</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
+        <v>7.8</v>
+      </c>
+      <c r="J4">
+        <v>3.65</v>
+      </c>
+      <c r="K4">
+        <v>4.1</v>
+      </c>
+      <c r="L4">
+        <v>1.48</v>
+      </c>
+      <c r="M4">
+        <v>1.1</v>
+      </c>
+      <c r="N4">
+        <v>2.84</v>
+      </c>
+      <c r="O4">
+        <v>1.45</v>
+      </c>
+      <c r="P4">
+        <v>1.61</v>
+      </c>
+      <c r="Q4">
+        <v>2.34</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
+        <v>4.5</v>
+      </c>
+      <c r="T4">
+        <v>2.28</v>
+      </c>
+      <c r="U4">
+        <v>1.65</v>
+      </c>
+      <c r="V4">
+        <v>1.15</v>
+      </c>
+      <c r="W4">
+        <v>2.38</v>
+      </c>
+      <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Y4">
+        <v>17.5</v>
+      </c>
+      <c r="Z4">
+        <v>60</v>
+      </c>
+      <c r="AA4">
+        <v>310</v>
+      </c>
+      <c r="AB4">
+        <v>6.4</v>
+      </c>
+      <c r="AC4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>30</v>
+      </c>
+      <c r="AE4">
+        <v>170</v>
+      </c>
+      <c r="AF4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG4">
+        <v>11.5</v>
+      </c>
+      <c r="AH4">
+        <v>38</v>
+      </c>
+      <c r="AI4">
+        <v>160</v>
+      </c>
+      <c r="AJ4">
+        <v>17.5</v>
+      </c>
+      <c r="AK4">
+        <v>23</v>
+      </c>
+      <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>270</v>
+      </c>
+      <c r="AN4">
+        <v>15</v>
+      </c>
+      <c r="AO4">
+        <v>290</v>
+      </c>
+      <c r="AP4">
+        <v>9.4</v>
+      </c>
+      <c r="AQ4">
+        <v>14.5</v>
+      </c>
+      <c r="AR4">
+        <v>8.6</v>
+      </c>
+      <c r="AS4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT4">
+        <v>5.5</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>7.4</v>
+      </c>
+      <c r="AW4">
+        <v>9.4</v>
+      </c>
+      <c r="AX4">
+        <v>7.2</v>
+      </c>
+      <c r="AY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>21</v>
+      </c>
+      <c r="BA4">
+        <v>9.4</v>
+      </c>
+      <c r="BB4">
+        <v>14</v>
+      </c>
+      <c r="BC4">
+        <v>18.5</v>
+      </c>
+      <c r="BD4">
+        <v>8.6</v>
+      </c>
+      <c r="BE4">
+        <v>9.6</v>
+      </c>
+      <c r="BF4">
+        <v>11</v>
+      </c>
+      <c r="BG4">
+        <v>9.6</v>
+      </c>
+      <c r="BH4">
+        <v>3.1</v>
+      </c>
+      <c r="BI4">
+        <v>2.7</v>
+      </c>
+      <c r="BJ4">
+        <v>13</v>
+      </c>
+      <c r="BK4">
+        <v>8.4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>22</v>
+      </c>
+      <c r="BN4">
+        <v>4</v>
+      </c>
+      <c r="BO4">
+        <v>3.4</v>
+      </c>
+      <c r="BP4">
+        <v>12.5</v>
+      </c>
+      <c r="BQ4">
+        <v>7.8</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>22</v>
+      </c>
+      <c r="BT4">
+        <v>11</v>
+      </c>
+      <c r="BU4">
+        <v>7.2</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>22</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>22</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>19</v>
+      </c>
+      <c r="CB4" t="s">
         <v>91</v>
-      </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>1.24</v>
-      </c>
-      <c r="Q4">
-        <v>1.01</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4">
-        <v>0</v>
-      </c>
-      <c r="BE4">
-        <v>0</v>
-      </c>
-      <c r="BF4">
-        <v>0</v>
-      </c>
-      <c r="BG4">
-        <v>0</v>
-      </c>
-      <c r="BH4">
-        <v>0</v>
-      </c>
-      <c r="BI4">
-        <v>0</v>
-      </c>
-      <c r="BJ4">
-        <v>0</v>
-      </c>
-      <c r="BK4">
-        <v>0</v>
-      </c>
-      <c r="BL4">
-        <v>0</v>
-      </c>
-      <c r="BM4">
-        <v>0</v>
-      </c>
-      <c r="BN4">
-        <v>0</v>
-      </c>
-      <c r="BO4">
-        <v>0</v>
-      </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>0</v>
-      </c>
-      <c r="BR4">
-        <v>0</v>
-      </c>
-      <c r="BS4">
-        <v>0</v>
-      </c>
-      <c r="BT4">
-        <v>0</v>
-      </c>
-      <c r="BU4">
-        <v>0</v>
-      </c>
-      <c r="BV4">
-        <v>0</v>
-      </c>
-      <c r="BW4">
-        <v>0</v>
-      </c>
-      <c r="BX4">
-        <v>0</v>
-      </c>
-      <c r="BY4">
-        <v>0</v>
-      </c>
-      <c r="BZ4">
-        <v>0</v>
-      </c>
-      <c r="CA4">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:80">
-      <c r="A5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5">
-        <v>4.4</v>
-      </c>
-      <c r="G5">
-        <v>5.5</v>
-      </c>
-      <c r="H5">
-        <v>1.99</v>
-      </c>
-      <c r="I5">
-        <v>2.18</v>
-      </c>
-      <c r="J5">
-        <v>2.96</v>
-      </c>
-      <c r="K5">
-        <v>3.4</v>
-      </c>
-      <c r="L5">
-        <v>1.47</v>
-      </c>
-      <c r="M5">
-        <v>1.12</v>
-      </c>
-      <c r="N5">
-        <v>2.62</v>
-      </c>
-      <c r="O5">
-        <v>1.51</v>
-      </c>
-      <c r="P5">
-        <v>1.52</v>
-      </c>
-      <c r="Q5">
-        <v>2.52</v>
-      </c>
-      <c r="R5">
-        <v>1.18</v>
-      </c>
-      <c r="S5">
-        <v>4.6</v>
-      </c>
-      <c r="T5">
-        <v>2.16</v>
-      </c>
-      <c r="U5">
-        <v>1.61</v>
-      </c>
-      <c r="V5">
-        <v>1.83</v>
-      </c>
-      <c r="W5">
-        <v>1.22</v>
-      </c>
-      <c r="X5">
-        <v>10.5</v>
-      </c>
-      <c r="Y5">
-        <v>8</v>
-      </c>
-      <c r="Z5">
-        <v>14</v>
-      </c>
-      <c r="AA5">
-        <v>32</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>13.5</v>
-      </c>
-      <c r="AE5">
-        <v>34</v>
-      </c>
-      <c r="AF5">
-        <v>44</v>
-      </c>
-      <c r="AG5">
-        <v>25</v>
-      </c>
-      <c r="AH5">
-        <v>30</v>
-      </c>
-      <c r="AI5">
-        <v>75</v>
-      </c>
-      <c r="AJ5">
-        <v>170</v>
-      </c>
-      <c r="AK5">
-        <v>110</v>
-      </c>
-      <c r="AL5">
-        <v>130</v>
-      </c>
-      <c r="AM5">
-        <v>250</v>
-      </c>
-      <c r="AN5">
-        <v>170</v>
-      </c>
-      <c r="AO5">
-        <v>32</v>
-      </c>
-      <c r="AP5">
-        <v>3.15</v>
-      </c>
-      <c r="AQ5">
-        <v>2.88</v>
-      </c>
-      <c r="AR5">
-        <v>3.4</v>
-      </c>
-      <c r="AS5">
-        <v>3.95</v>
-      </c>
-      <c r="AT5">
-        <v>3.45</v>
-      </c>
-      <c r="AU5">
-        <v>3</v>
-      </c>
-      <c r="AV5">
-        <v>3.35</v>
-      </c>
-      <c r="AW5">
-        <v>4</v>
-      </c>
-      <c r="AX5">
-        <v>4.1</v>
-      </c>
-      <c r="AY5">
-        <v>3.8</v>
-      </c>
-      <c r="AZ5">
-        <v>3.9</v>
-      </c>
-      <c r="BA5">
-        <v>4.2</v>
-      </c>
-      <c r="BB5">
-        <v>4.4</v>
-      </c>
-      <c r="BC5">
-        <v>4.3</v>
-      </c>
-      <c r="BD5">
-        <v>4.3</v>
-      </c>
-      <c r="BE5">
-        <v>4.4</v>
-      </c>
-      <c r="BF5">
-        <v>4.4</v>
-      </c>
-      <c r="BG5">
-        <v>3.95</v>
-      </c>
-      <c r="BH5">
-        <v>3.15</v>
-      </c>
-      <c r="BI5">
-        <v>2.26</v>
-      </c>
-      <c r="BJ5">
-        <v>14</v>
-      </c>
-      <c r="BK5">
-        <v>3.75</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>5</v>
-      </c>
-      <c r="BN5">
-        <v>9.4</v>
-      </c>
-      <c r="BO5">
-        <v>5.8</v>
-      </c>
-      <c r="BP5">
-        <v>60</v>
-      </c>
-      <c r="BQ5">
-        <v>4.7</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>4.8</v>
-      </c>
-      <c r="BT5">
-        <v>5.3</v>
-      </c>
-      <c r="BU5">
-        <v>3.5</v>
-      </c>
-      <c r="BV5">
-        <v>20</v>
-      </c>
-      <c r="BW5">
-        <v>4</v>
-      </c>
-      <c r="BX5">
-        <v>48</v>
-      </c>
-      <c r="BY5">
-        <v>4.6</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80">
-      <c r="A6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6">
-        <v>1.36</v>
-      </c>
-      <c r="G6">
-        <v>1.37</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>13.5</v>
-      </c>
-      <c r="J6">
-        <v>5.3</v>
-      </c>
-      <c r="K6">
-        <v>5.7</v>
-      </c>
-      <c r="L6">
-        <v>1.34</v>
-      </c>
-      <c r="M6">
-        <v>1.04</v>
-      </c>
-      <c r="N6">
-        <v>4.4</v>
-      </c>
-      <c r="O6">
-        <v>1.25</v>
-      </c>
-      <c r="P6">
-        <v>2.16</v>
-      </c>
-      <c r="Q6">
-        <v>1.77</v>
-      </c>
-      <c r="R6">
-        <v>1.44</v>
-      </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-      <c r="T6">
-        <v>2.08</v>
-      </c>
-      <c r="U6">
-        <v>1.76</v>
-      </c>
-      <c r="V6">
-        <v>1.08</v>
-      </c>
-      <c r="W6">
-        <v>3.7</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6">
-        <v>1.01</v>
-      </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>1.01</v>
-      </c>
-      <c r="AU6">
-        <v>1.01</v>
-      </c>
-      <c r="AV6">
-        <v>1.01</v>
-      </c>
-      <c r="AW6">
-        <v>1.01</v>
-      </c>
-      <c r="AX6">
-        <v>1.01</v>
-      </c>
-      <c r="AY6">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6">
-        <v>1.01</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>1.01</v>
-      </c>
-      <c r="BC6">
-        <v>1.01</v>
-      </c>
-      <c r="BD6">
-        <v>1.01</v>
-      </c>
-      <c r="BE6">
-        <v>1.01</v>
-      </c>
-      <c r="BF6">
-        <v>1.01</v>
-      </c>
-      <c r="BG6">
-        <v>1.01</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.04</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.04</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.04</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 18:57:53</t>
+    <t>2026-08-10 21:05:03</t>
   </si>
 </sst>
 </file>
@@ -883,43 +883,43 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
         <v>2.9</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>1.7</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>7.2</v>
@@ -934,7 +934,7 @@
         <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
         <v>7.2</v>
@@ -976,13 +976,13 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
         <v>90</v>
       </c>
       <c r="AM2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN2">
         <v>55</v>
@@ -1003,7 +1003,7 @@
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1012,7 +1012,7 @@
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1048,61 +1048,61 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BJ2">
         <v>18</v>
       </c>
       <c r="BK2">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BN2">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="BP2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="BT2">
         <v>9.6</v>
       </c>
       <c r="BU2">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="CB2" t="s">
         <v>91</v>
@@ -1125,22 +1125,22 @@
         <v>89</v>
       </c>
       <c r="F3">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G3">
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
         <v>2.88</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1149,28 +1149,28 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
         <v>1.53</v>
@@ -1182,7 +1182,7 @@
         <v>11</v>
       </c>
       <c r="Y3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3">
         <v>18</v>
@@ -1191,7 +1191,7 @@
         <v>46</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
@@ -1212,10 +1212,10 @@
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK3">
         <v>42</v>
@@ -1227,25 +1227,25 @@
         <v>150</v>
       </c>
       <c r="AN3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AO3">
         <v>38</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1254,7 +1254,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
@@ -1263,28 +1263,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC3">
         <v>32</v>
       </c>
       <c r="BD3">
+        <v>8.4</v>
+      </c>
+      <c r="BE3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
         <v>7.8</v>
-      </c>
-      <c r="BE3">
-        <v>8.6</v>
-      </c>
-      <c r="BF3">
-        <v>32</v>
-      </c>
-      <c r="BG3">
-        <v>7.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1370,19 +1370,19 @@
         <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H4">
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.48</v>
@@ -1391,25 +1391,25 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
         <v>1.22</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
         <v>1.65</v>
@@ -1469,22 +1469,22 @@
         <v>270</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
         <v>290</v>
       </c>
       <c r="AP4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS4">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
         <v>5.5</v>
@@ -1493,10 +1493,10 @@
         <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AW4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4">
         <v>7.2</v>
@@ -1508,7 +1508,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
         <v>14</v>
@@ -1517,19 +1517,19 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
         <v>11</v>
       </c>
       <c r="BG4">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
         <v>2.7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -289,7 +289,7 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 21:05:03</t>
+    <t>2026-08-10 23:12:02</t>
   </si>
 </sst>
 </file>
@@ -883,67 +883,67 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O2">
         <v>1.7</v>
       </c>
       <c r="P2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q2">
         <v>3.15</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S2">
         <v>7.2</v>
       </c>
       <c r="T2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
+        <v>1.65</v>
+      </c>
+      <c r="V2">
+        <v>1.35</v>
+      </c>
+      <c r="W2">
         <v>1.63</v>
-      </c>
-      <c r="V2">
-        <v>1.34</v>
-      </c>
-      <c r="W2">
-        <v>1.65</v>
       </c>
       <c r="X2">
         <v>7.2</v>
       </c>
       <c r="Y2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -952,40 +952,40 @@
         <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
         <v>14</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL2">
         <v>90</v>
       </c>
       <c r="AM2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -997,13 +997,13 @@
         <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1012,19 +1012,19 @@
         <v>16</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB2">
         <v>29</v>
@@ -1033,7 +1033,7 @@
         <v>29</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>90</v>
@@ -1042,67 +1042,67 @@
         <v>30</v>
       </c>
       <c r="BG2">
+        <v>38</v>
+      </c>
+      <c r="BH2">
+        <v>2.5</v>
+      </c>
+      <c r="BI2">
+        <v>2.22</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2">
+        <v>7.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>12</v>
+      </c>
+      <c r="BN2">
+        <v>5.4</v>
+      </c>
+      <c r="BO2">
+        <v>4.5</v>
+      </c>
+      <c r="BP2">
+        <v>26</v>
+      </c>
+      <c r="BQ2">
+        <v>8.4</v>
+      </c>
+      <c r="BR2">
+        <v>60</v>
+      </c>
+      <c r="BS2">
+        <v>10.5</v>
+      </c>
+      <c r="BT2">
+        <v>6.8</v>
+      </c>
+      <c r="BU2">
+        <v>5.5</v>
+      </c>
+      <c r="BV2">
         <v>40</v>
       </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.24</v>
-      </c>
-      <c r="BJ2">
-        <v>18</v>
-      </c>
-      <c r="BK2">
-        <v>1.16</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.24</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.24</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.24</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.22</v>
-      </c>
-      <c r="BT2">
+      <c r="BW2">
         <v>9.6</v>
       </c>
-      <c r="BU2">
-        <v>1.1</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.24</v>
-      </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY2">
-        <v>1.23</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="CA2">
-        <v>1.23</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>91</v>
@@ -1125,19 +1125,19 @@
         <v>89</v>
       </c>
       <c r="F3">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
         <v>3.25</v>
@@ -1146,40 +1146,40 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>9.199999999999999</v>
@@ -1194,7 +1194,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
         <v>13.5</v>
@@ -1206,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>21</v>
@@ -1218,10 +1218,10 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM3">
         <v>150</v>
@@ -1230,121 +1230,121 @@
         <v>50</v>
       </c>
       <c r="AO3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP3">
         <v>8.6</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
         <v>17.5</v>
       </c>
       <c r="BA3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB3">
         <v>8.6</v>
-      </c>
-      <c r="BB3">
-        <v>8.4</v>
       </c>
       <c r="BC3">
         <v>32</v>
       </c>
       <c r="BD3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE3">
+        <v>9.6</v>
+      </c>
+      <c r="BF3">
         <v>8.4</v>
       </c>
-      <c r="BE3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>91</v>
@@ -1367,7 +1367,7 @@
         <v>90</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
         <v>1.73</v>
@@ -1394,22 +1394,22 @@
         <v>2.78</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
         <v>1.65</v>
@@ -1421,10 +1421,10 @@
         <v>2.38</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z4">
         <v>60</v>
@@ -1469,37 +1469,37 @@
         <v>270</v>
       </c>
       <c r="AN4">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO4">
         <v>290</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4">
         <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AW4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
@@ -1508,7 +1508,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB4">
         <v>14</v>
@@ -1517,16 +1517,16 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4">
         <v>11</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
@@ -1544,7 +1544,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>4</v>
@@ -1562,7 +1562,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
         <v>11</v>
@@ -1574,19 +1574,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>91</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
     <t>Talleres</t>
   </si>
   <si>
@@ -280,6 +283,12 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>CA Platense</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -289,7 +298,13 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
-    <t>2026-08-10 23:12:02</t>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
+    <t>2026-08-11 01:19:23</t>
   </si>
 </sst>
 </file>
@@ -621,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -877,79 +892,79 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
         <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
         <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
@@ -964,28 +979,28 @@
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -994,22 +1009,22 @@
         <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS2">
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW2">
         <v>32</v>
@@ -1018,7 +1033,7 @@
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
         <v>24</v>
@@ -1036,7 +1051,7 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="BF2">
         <v>30</v>
@@ -1045,13 +1060,13 @@
         <v>38</v>
       </c>
       <c r="BH2">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1060,25 +1075,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1090,22 +1105,22 @@
         <v>40</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1119,10 +1134,10 @@
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -1137,13 +1152,13 @@
         <v>2.82</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1161,7 +1176,7 @@
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
         <v>4.7</v>
@@ -1173,7 +1188,7 @@
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
         <v>1.45</v>
@@ -1347,7 +1362,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1361,52 +1376,52 @@
         <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>2.32</v>
@@ -1415,10 +1430,10 @@
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1487,7 +1502,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU4">
         <v>7.6</v>
@@ -1502,10 +1517,10 @@
         <v>7.4</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA4">
         <v>9.6</v>
@@ -1589,7 +1604,491 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>91</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>1.94</v>
+      </c>
+      <c r="G5">
+        <v>2.02</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5.6</v>
+      </c>
+      <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
+        <v>3.35</v>
+      </c>
+      <c r="L5">
+        <v>1.55</v>
+      </c>
+      <c r="M5">
+        <v>1.14</v>
+      </c>
+      <c r="N5">
+        <v>2.48</v>
+      </c>
+      <c r="O5">
+        <v>1.6</v>
+      </c>
+      <c r="P5">
+        <v>1.52</v>
+      </c>
+      <c r="Q5">
+        <v>2.78</v>
+      </c>
+      <c r="R5">
+        <v>1.18</v>
+      </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
+      <c r="T5">
+        <v>2.36</v>
+      </c>
+      <c r="U5">
+        <v>1.65</v>
+      </c>
+      <c r="V5">
+        <v>1.22</v>
+      </c>
+      <c r="W5">
+        <v>1.98</v>
+      </c>
+      <c r="X5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>12.5</v>
+      </c>
+      <c r="Z5">
+        <v>48</v>
+      </c>
+      <c r="AA5">
+        <v>210</v>
+      </c>
+      <c r="AB5">
+        <v>6.2</v>
+      </c>
+      <c r="AC5">
+        <v>7.8</v>
+      </c>
+      <c r="AD5">
+        <v>23</v>
+      </c>
+      <c r="AE5">
+        <v>140</v>
+      </c>
+      <c r="AF5">
+        <v>12.5</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>36</v>
+      </c>
+      <c r="AI5">
+        <v>170</v>
+      </c>
+      <c r="AJ5">
+        <v>30</v>
+      </c>
+      <c r="AK5">
+        <v>36</v>
+      </c>
+      <c r="AL5">
+        <v>85</v>
+      </c>
+      <c r="AM5">
+        <v>320</v>
+      </c>
+      <c r="AN5">
+        <v>34</v>
+      </c>
+      <c r="AO5">
+        <v>250</v>
+      </c>
+      <c r="AP5">
+        <v>7.2</v>
+      </c>
+      <c r="AQ5">
+        <v>10.5</v>
+      </c>
+      <c r="AR5">
+        <v>6.8</v>
+      </c>
+      <c r="AS5">
+        <v>7.6</v>
+      </c>
+      <c r="AT5">
+        <v>5.5</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>5.9</v>
+      </c>
+      <c r="AW5">
+        <v>7.4</v>
+      </c>
+      <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>6.4</v>
+      </c>
+      <c r="BA5">
+        <v>7.4</v>
+      </c>
+      <c r="BB5">
+        <v>21</v>
+      </c>
+      <c r="BC5">
+        <v>6.4</v>
+      </c>
+      <c r="BD5">
+        <v>7.2</v>
+      </c>
+      <c r="BE5">
+        <v>7.6</v>
+      </c>
+      <c r="BF5">
+        <v>19.5</v>
+      </c>
+      <c r="BG5">
+        <v>7.6</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.04</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.04</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.04</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.04</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.04</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.04</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.04</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.04</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.04</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.04</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6">
+        <v>1.31</v>
+      </c>
+      <c r="G6">
+        <v>1.35</v>
+      </c>
+      <c r="H6">
+        <v>12.5</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>5.4</v>
+      </c>
+      <c r="K6">
+        <v>6.2</v>
+      </c>
+      <c r="L6">
+        <v>1.4</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.6</v>
+      </c>
+      <c r="O6">
+        <v>1.34</v>
+      </c>
+      <c r="P6">
+        <v>1.88</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>1.33</v>
+      </c>
+      <c r="S6">
+        <v>3.6</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.53</v>
+      </c>
+      <c r="V6">
+        <v>1.06</v>
+      </c>
+      <c r="W6">
+        <v>3.85</v>
+      </c>
+      <c r="X6">
+        <v>18.5</v>
+      </c>
+      <c r="Y6">
+        <v>38</v>
+      </c>
+      <c r="Z6">
+        <v>170</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>6.6</v>
+      </c>
+      <c r="AC6">
+        <v>14</v>
+      </c>
+      <c r="AD6">
+        <v>65</v>
+      </c>
+      <c r="AE6">
+        <v>440</v>
+      </c>
+      <c r="AF6">
+        <v>6.8</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>46</v>
+      </c>
+      <c r="AI6">
+        <v>330</v>
+      </c>
+      <c r="AJ6">
+        <v>12</v>
+      </c>
+      <c r="AK6">
+        <v>18.5</v>
+      </c>
+      <c r="AL6">
+        <v>65</v>
+      </c>
+      <c r="AM6">
+        <v>470</v>
+      </c>
+      <c r="AN6">
+        <v>7.4</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6">
+        <v>6.4</v>
+      </c>
+      <c r="AR6">
+        <v>7.4</v>
+      </c>
+      <c r="AS6">
+        <v>7.8</v>
+      </c>
+      <c r="AT6">
+        <v>5.7</v>
+      </c>
+      <c r="AU6">
+        <v>11.5</v>
+      </c>
+      <c r="AV6">
+        <v>6.8</v>
+      </c>
+      <c r="AW6">
+        <v>7.6</v>
+      </c>
+      <c r="AX6">
+        <v>5.9</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>6.6</v>
+      </c>
+      <c r="BA6">
+        <v>7.6</v>
+      </c>
+      <c r="BB6">
+        <v>8.6</v>
+      </c>
+      <c r="BC6">
+        <v>15.5</v>
+      </c>
+      <c r="BD6">
+        <v>6.8</v>
+      </c>
+      <c r="BE6">
+        <v>7.6</v>
+      </c>
+      <c r="BF6">
+        <v>5.4</v>
+      </c>
+      <c r="BG6">
+        <v>7.8</v>
+      </c>
+      <c r="BH6">
+        <v>3.5</v>
+      </c>
+      <c r="BI6">
+        <v>2.88</v>
+      </c>
+      <c r="BJ6">
+        <v>15.5</v>
+      </c>
+      <c r="BK6">
+        <v>8</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>15.5</v>
+      </c>
+      <c r="BN6">
+        <v>3.4</v>
+      </c>
+      <c r="BO6">
+        <v>2.82</v>
+      </c>
+      <c r="BP6">
+        <v>7.8</v>
+      </c>
+      <c r="BQ6">
+        <v>5.8</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>10.5</v>
+      </c>
+      <c r="BT6">
+        <v>17</v>
+      </c>
+      <c r="BU6">
+        <v>8.4</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>15</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>15</v>
+      </c>
+      <c r="BZ6">
+        <v>16</v>
+      </c>
+      <c r="CA6">
+        <v>8</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -304,7 +304,7 @@
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>2026-08-11 01:19:23</t>
+    <t>2026-08-11 03:26:12</t>
   </si>
 </sst>
 </file>
@@ -898,67 +898,67 @@
         <v>91</v>
       </c>
       <c r="F2">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
         <v>2.6</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
         <v>3.75</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="M2">
+        <v>1.15</v>
+      </c>
+      <c r="N2">
+        <v>2.46</v>
+      </c>
+      <c r="O2">
+        <v>1.65</v>
+      </c>
+      <c r="P2">
+        <v>1.48</v>
+      </c>
+      <c r="Q2">
+        <v>2.96</v>
+      </c>
+      <c r="R2">
         <v>1.16</v>
       </c>
-      <c r="N2">
-        <v>2.38</v>
-      </c>
-      <c r="O2">
-        <v>1.68</v>
-      </c>
-      <c r="P2">
-        <v>1.44</v>
-      </c>
-      <c r="Q2">
-        <v>3.1</v>
-      </c>
-      <c r="R2">
-        <v>1.15</v>
-      </c>
       <c r="S2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.62</v>
       </c>
       <c r="X2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -970,16 +970,16 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <v>29</v>
@@ -988,7 +988,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK2">
         <v>42</v>
@@ -997,7 +997,7 @@
         <v>1000</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AN2">
         <v>50</v>
@@ -1009,13 +1009,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR2">
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1027,16 +1027,16 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX2">
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA2">
         <v>40</v>
@@ -1051,22 +1051,22 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>2.58</v>
       </c>
       <c r="BI2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>7.6</v>
@@ -1075,25 +1075,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
         <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1102,22 +1102,22 @@
         <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
         <v>96</v>
@@ -1140,7 +1140,7 @@
         <v>92</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
         <v>3.2</v>
@@ -1152,7 +1152,7 @@
         <v>2.82</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
         <v>3.25</v>
@@ -1170,13 +1170,13 @@
         <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>4.7</v>
@@ -1188,7 +1188,7 @@
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.45</v>
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="Y3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z3">
         <v>18</v>
@@ -1257,7 +1257,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
@@ -1269,7 +1269,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
@@ -1281,85 +1281,85 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
+        <v>9</v>
+      </c>
+      <c r="BB3">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB3">
-        <v>8.6</v>
       </c>
       <c r="BC3">
         <v>32</v>
       </c>
       <c r="BD3">
+        <v>9</v>
+      </c>
+      <c r="BE3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF3">
+        <v>8.6</v>
+      </c>
+      <c r="BG3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH3">
+        <v>3.05</v>
+      </c>
+      <c r="BI3">
+        <v>2.46</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>5.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>10</v>
+      </c>
+      <c r="BN3">
+        <v>6.2</v>
+      </c>
+      <c r="BO3">
+        <v>4.7</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>7.8</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE3">
-        <v>9.6</v>
-      </c>
-      <c r="BF3">
-        <v>8.4</v>
-      </c>
-      <c r="BG3">
-        <v>8</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>
@@ -1382,46 +1382,46 @@
         <v>93</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="O4">
         <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T4">
         <v>2.32</v>
@@ -1430,10 +1430,10 @@
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1493,7 +1493,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR4">
         <v>8.800000000000001</v>
@@ -1544,7 +1544,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI4">
         <v>2.7</v>
@@ -1559,7 +1559,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>4</v>
@@ -1577,7 +1577,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT4">
         <v>11</v>
@@ -1589,19 +1589,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="s">
         <v>96</v>
@@ -1642,13 +1642,13 @@
         <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="M5">
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O5">
         <v>1.6</v>
@@ -1657,7 +1657,7 @@
         <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1678,7 +1678,7 @@
         <v>1.98</v>
       </c>
       <c r="X5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>12.5</v>
@@ -1741,7 +1741,7 @@
         <v>6.8</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>5.5</v>
@@ -1750,10 +1750,10 @@
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1762,88 +1762,88 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
         <v>21</v>
       </c>
       <c r="BC5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
         <v>19.5</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="CB5" t="s">
         <v>96</v>
@@ -1869,7 +1869,7 @@
         <v>1.31</v>
       </c>
       <c r="G6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H6">
         <v>12.5</v>
@@ -1878,13 +1878,13 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
         <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -1896,13 +1896,13 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q6">
         <v>2</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
         <v>3.6</v>
@@ -1917,7 +1917,7 @@
         <v>1.06</v>
       </c>
       <c r="W6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X6">
         <v>18.5</v>
@@ -1935,19 +1935,19 @@
         <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD6">
         <v>65</v>
       </c>
       <c r="AE6">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AF6">
         <v>6.8</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH6">
         <v>46</v>
@@ -1959,7 +1959,7 @@
         <v>12</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AL6">
         <v>65</v>
@@ -1974,16 +1974,16 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AR6">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AS6">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
@@ -1992,10 +1992,10 @@
         <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW6">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6">
         <v>5.9</v>
@@ -2004,10 +2004,10 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA6">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
         <v>8.6</v>
@@ -2016,76 +2016,76 @@
         <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
         <v>5.4</v>
       </c>
       <c r="BG6">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH6">
         <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6">
         <v>15.5</v>
       </c>
       <c r="BK6">
+        <v>7.2</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>13</v>
+      </c>
+      <c r="BN6">
+        <v>3.45</v>
+      </c>
+      <c r="BO6">
+        <v>2.76</v>
+      </c>
+      <c r="BP6">
         <v>8</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>15.5</v>
-      </c>
-      <c r="BN6">
-        <v>3.4</v>
-      </c>
-      <c r="BO6">
-        <v>2.82</v>
-      </c>
-      <c r="BP6">
-        <v>7.8</v>
       </c>
       <c r="BQ6">
         <v>5.8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
         <v>17</v>
       </c>
       <c r="BU6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -304,7 +304,7 @@
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>2026-08-11 03:26:12</t>
+    <t>2026-08-11 05:33:11</t>
   </si>
 </sst>
 </file>
@@ -901,16 +901,16 @@
         <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H2">
         <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.05</v>
@@ -919,58 +919,58 @@
         <v>1.64</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y2">
+        <v>10</v>
+      </c>
+      <c r="Z2">
+        <v>24</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
         <v>7.4</v>
-      </c>
-      <c r="Y2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z2">
-        <v>23</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>7</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
         <v>75</v>
@@ -979,34 +979,34 @@
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM2">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
         <v>8.4</v>
@@ -1018,16 +1018,16 @@
         <v>32</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1036,10 +1036,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB2">
         <v>29</v>
@@ -1048,10 +1048,10 @@
         <v>29</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF2">
         <v>30</v>
@@ -1063,7 +1063,7 @@
         <v>2.58</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1087,7 +1087,7 @@
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>55</v>
@@ -1111,10 +1111,10 @@
         <v>100</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA2">
         <v>11</v>
@@ -1143,31 +1143,31 @@
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
         <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.62</v>
@@ -1176,190 +1176,190 @@
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>1.05</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
         <v>1.55</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AE3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8.6</v>
+        <v>1.78</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>1.96</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>2.14</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>1.93</v>
       </c>
       <c r="AW3">
-        <v>8.199999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="AX3">
-        <v>16.5</v>
+        <v>2</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>1.96</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>2.02</v>
       </c>
       <c r="BA3">
-        <v>9</v>
+        <v>2.14</v>
       </c>
       <c r="BB3">
-        <v>8.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>2.14</v>
       </c>
       <c r="BD3">
-        <v>9</v>
+        <v>2.14</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>2.14</v>
       </c>
       <c r="BG3">
-        <v>8.199999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>96</v>
@@ -1382,58 +1382,58 @@
         <v>93</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>7.4</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1493,7 +1493,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
         <v>8.800000000000001</v>
@@ -1648,7 +1648,7 @@
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
         <v>1.6</v>
@@ -1696,7 +1696,7 @@
         <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE5">
         <v>140</v>
@@ -1711,7 +1711,7 @@
         <v>36</v>
       </c>
       <c r="AI5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ5">
         <v>30</v>
@@ -1884,7 +1884,7 @@
         <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -1896,13 +1896,13 @@
         <v>1.34</v>
       </c>
       <c r="P6">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q6">
         <v>2</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
         <v>3.6</v>
@@ -1950,7 +1950,7 @@
         <v>14</v>
       </c>
       <c r="AH6">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AI6">
         <v>330</v>
@@ -2031,61 +2031,61 @@
         <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6">
         <v>15.5</v>
       </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BO6">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BP6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BQ6">
         <v>5.8</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
         <v>17</v>
       </c>
       <c r="BU6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -304,7 +304,7 @@
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>2026-08-11 05:33:11</t>
+    <t>2026-08-11 07:40:26</t>
   </si>
 </sst>
 </file>
@@ -901,37 +901,37 @@
         <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
         <v>1.18</v>
@@ -940,49 +940,49 @@
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
         <v>8.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2">
         <v>24</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2">
+        <v>7.6</v>
+      </c>
+      <c r="AC2">
         <v>7.4</v>
-      </c>
-      <c r="AC2">
-        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -994,13 +994,13 @@
         <v>38</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1009,13 +1009,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1024,58 +1024,58 @@
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA2">
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH2">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BI2">
         <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1087,13 +1087,13 @@
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1105,19 +1105,19 @@
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>96</v>
@@ -1146,13 +1146,13 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.25</v>
@@ -1161,40 +1161,40 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
         <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
         <v>1.05</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1254,52 +1254,52 @@
         <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AS3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AT3">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AU3">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AV3">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AW3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AX3">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AY3">
-        <v>1.96</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="BA3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BB3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BC3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BD3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BE3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BF3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BG3">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1382,178 +1382,178 @@
         <v>93</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="G4">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M4">
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
+        <v>1.6</v>
+      </c>
+      <c r="Q4">
+        <v>2.56</v>
+      </c>
+      <c r="R4">
+        <v>1.21</v>
+      </c>
+      <c r="S4">
+        <v>5.3</v>
+      </c>
+      <c r="T4">
+        <v>2.36</v>
+      </c>
+      <c r="U4">
         <v>1.64</v>
       </c>
-      <c r="Q4">
-        <v>2.46</v>
-      </c>
-      <c r="R4">
-        <v>1.23</v>
-      </c>
-      <c r="S4">
-        <v>5</v>
-      </c>
-      <c r="T4">
-        <v>2.38</v>
-      </c>
-      <c r="U4">
-        <v>1.65</v>
-      </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z4">
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE4">
+        <v>160</v>
+      </c>
+      <c r="AF4">
+        <v>9</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>36</v>
+      </c>
+      <c r="AI4">
         <v>170</v>
       </c>
-      <c r="AF4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>38</v>
-      </c>
-      <c r="AI4">
-        <v>160</v>
-      </c>
       <c r="AJ4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO4">
         <v>290</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AS4">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>7.4</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BB4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BE4">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BG4">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1562,34 +1562,34 @@
         <v>11.5</v>
       </c>
       <c r="BN4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1598,10 +1598,10 @@
         <v>10.5</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>96</v>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
         <v>3.15</v>
@@ -1642,19 +1642,19 @@
         <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O5">
         <v>1.6</v>
       </c>
       <c r="P5">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
         <v>2.8</v>
@@ -1675,10 +1675,10 @@
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5">
         <v>12.5</v>
@@ -1741,7 +1741,7 @@
         <v>6.8</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
         <v>5.5</v>
@@ -1750,10 +1750,10 @@
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1762,28 +1762,28 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB5">
         <v>21</v>
       </c>
       <c r="BC5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
         <v>19.5</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>2.62</v>
@@ -1801,13 +1801,13 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.28</v>
+        <v>17.5</v>
       </c>
       <c r="BN5">
         <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
         <v>16.5</v>
@@ -1837,7 +1837,7 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>2.24</v>
+        <v>15</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -1869,16 +1869,16 @@
         <v>1.31</v>
       </c>
       <c r="G6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H6">
         <v>12.5</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K6">
         <v>6.2</v>
@@ -1890,7 +1890,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>1.34</v>
@@ -1899,7 +1899,7 @@
         <v>1.88</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R6">
         <v>1.33</v>
@@ -1908,7 +1908,7 @@
         <v>3.6</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
         <v>1.53</v>
@@ -1917,7 +1917,7 @@
         <v>1.06</v>
       </c>
       <c r="W6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X6">
         <v>18.5</v>
@@ -1935,55 +1935,55 @@
         <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AD6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE6">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AF6">
         <v>6.8</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AI6">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AJ6">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL6">
         <v>65</v>
       </c>
       <c r="AM6">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AN6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AT6">
         <v>5.7</v>
@@ -1992,10 +1992,10 @@
         <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AW6">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
         <v>5.9</v>
@@ -2004,10 +2004,10 @@
         <v>10</v>
       </c>
       <c r="AZ6">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA6">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB6">
         <v>8.6</v>
@@ -2016,22 +2016,22 @@
         <v>15.5</v>
       </c>
       <c r="BD6">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6">
         <v>6.2</v>
       </c>
-      <c r="BF6">
-        <v>5.4</v>
-      </c>
       <c r="BG6">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>15.5</v>
@@ -2043,7 +2043,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN6">
         <v>3.4</v>
@@ -2061,7 +2061,7 @@
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT6">
         <v>17</v>
@@ -2085,7 +2085,7 @@
         <v>16</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
         <v>96</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="113">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,12 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>2026-08-12</t>
   </si>
   <si>
@@ -271,6 +277,12 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -283,12 +295,30 @@
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>Milford</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Durban City</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
     <t>SE Palmeiras</t>
   </si>
   <si>
+    <t>Deportes Recoleta</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -298,13 +328,31 @@
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
+    <t>Siwelele FC</t>
+  </si>
+  <si>
+    <t>Sekhukhune United</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Orlando Pirates (SA)</t>
+  </si>
+  <si>
+    <t>Cobreloa Calama</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>2026-08-11 07:40:26</t>
+    <t>CSD Rangers</t>
+  </si>
+  <si>
+    <t>2026-08-11 09:48:01</t>
   </si>
 </sst>
 </file>
@@ -636,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -886,22 +934,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F2">
         <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H2">
         <v>3.65</v>
@@ -913,37 +961,37 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T2">
         <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -952,22 +1000,22 @@
         <v>1.64</v>
       </c>
       <c r="X2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
         <v>9.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA2">
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -979,10 +1027,10 @@
         <v>15</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -994,28 +1042,28 @@
         <v>38</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2">
         <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR2">
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1027,7 +1075,7 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1036,91 +1084,91 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BB2">
         <v>30</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BH2">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1128,31 +1176,31 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F3">
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
         <v>2.6</v>
       </c>
       <c r="I3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
         <v>3.25</v>
@@ -1161,31 +1209,31 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V3">
         <v>1.56</v>
@@ -1194,7 +1242,7 @@
         <v>1.43</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1248,58 +1296,58 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AQ3">
         <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AS3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AT3">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AU3">
-        <v>1.49</v>
+        <v>6</v>
       </c>
       <c r="AV3">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="AW3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AX3">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="AZ3">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="BA3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BB3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BC3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BD3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BE3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BF3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BG3">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1362,7 +1410,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1370,28 +1418,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G4">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
         <v>3.6</v>
@@ -1400,22 +1448,22 @@
         <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P4">
         <v>1.6</v>
       </c>
       <c r="Q4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>1.21</v>
@@ -1427,49 +1475,49 @@
         <v>2.36</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB4">
         <v>6.2</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>29</v>
       </c>
       <c r="AE4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
         <v>19</v>
@@ -1478,55 +1526,55 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AP4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
         <v>38</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>23</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC4">
         <v>19.5</v>
@@ -1535,40 +1583,40 @@
         <v>17</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF4">
         <v>14.5</v>
       </c>
       <c r="BG4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
         <v>6.2</v>
@@ -1577,25 +1625,25 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT4">
         <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1604,491 +1652,1943 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F5">
-        <v>1.94</v>
+        <v>2.98</v>
       </c>
       <c r="G5">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="O5">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
+        <v>1.41</v>
+      </c>
+      <c r="Q5">
+        <v>2.66</v>
+      </c>
+      <c r="R5">
+        <v>1.16</v>
+      </c>
+      <c r="S5">
+        <v>1.02</v>
+      </c>
+      <c r="T5">
+        <v>1.98</v>
+      </c>
+      <c r="U5">
+        <v>1.64</v>
+      </c>
+      <c r="V5">
         <v>1.49</v>
       </c>
-      <c r="Q5">
-        <v>2.8</v>
-      </c>
-      <c r="R5">
-        <v>1.18</v>
-      </c>
-      <c r="S5">
-        <v>6</v>
-      </c>
-      <c r="T5">
-        <v>2.36</v>
-      </c>
-      <c r="U5">
-        <v>1.65</v>
-      </c>
-      <c r="V5">
-        <v>1.22</v>
-      </c>
       <c r="W5">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z5">
+        <v>19.5</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y5">
-        <v>12.5</v>
-      </c>
-      <c r="Z5">
-        <v>48</v>
-      </c>
-      <c r="AA5">
-        <v>210</v>
-      </c>
-      <c r="AB5">
-        <v>6.2</v>
-      </c>
-      <c r="AC5">
-        <v>7.8</v>
-      </c>
       <c r="AD5">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
+        <v>18.5</v>
+      </c>
+      <c r="AH5">
+        <v>29</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5">
+        <v>1.03</v>
+      </c>
+      <c r="AR5">
+        <v>1.03</v>
+      </c>
+      <c r="AS5">
+        <v>1.03</v>
+      </c>
+      <c r="AT5">
+        <v>1.03</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.03</v>
+      </c>
+      <c r="AW5">
+        <v>1.03</v>
+      </c>
+      <c r="AX5">
+        <v>1.03</v>
+      </c>
+      <c r="AY5">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5">
+        <v>1.03</v>
+      </c>
+      <c r="BA5">
+        <v>1.03</v>
+      </c>
+      <c r="BB5">
+        <v>1.03</v>
+      </c>
+      <c r="BC5">
+        <v>1.03</v>
+      </c>
+      <c r="BD5">
+        <v>1.03</v>
+      </c>
+      <c r="BE5">
+        <v>1.03</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>2.68</v>
+      </c>
+      <c r="BI5">
+        <v>2.22</v>
+      </c>
+      <c r="BJ5">
         <v>12</v>
       </c>
-      <c r="AH5">
-        <v>36</v>
-      </c>
-      <c r="AI5">
-        <v>160</v>
-      </c>
-      <c r="AJ5">
-        <v>30</v>
-      </c>
-      <c r="AK5">
-        <v>36</v>
-      </c>
-      <c r="AL5">
-        <v>85</v>
-      </c>
-      <c r="AM5">
-        <v>320</v>
-      </c>
-      <c r="AN5">
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>6.4</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
         <v>34</v>
       </c>
-      <c r="AO5">
-        <v>250</v>
-      </c>
-      <c r="AP5">
-        <v>7.2</v>
-      </c>
-      <c r="AQ5">
-        <v>10.5</v>
-      </c>
-      <c r="AR5">
-        <v>6.8</v>
-      </c>
-      <c r="AS5">
-        <v>7.6</v>
-      </c>
-      <c r="AT5">
-        <v>5.5</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>17</v>
-      </c>
-      <c r="AW5">
-        <v>7.4</v>
-      </c>
-      <c r="AX5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY5">
-        <v>10</v>
-      </c>
-      <c r="AZ5">
-        <v>6.4</v>
-      </c>
-      <c r="BA5">
-        <v>7.4</v>
-      </c>
-      <c r="BB5">
-        <v>21</v>
-      </c>
-      <c r="BC5">
-        <v>6.4</v>
-      </c>
-      <c r="BD5">
-        <v>7.2</v>
-      </c>
-      <c r="BE5">
-        <v>7.6</v>
-      </c>
-      <c r="BF5">
-        <v>19.5</v>
-      </c>
-      <c r="BG5">
-        <v>7.6</v>
-      </c>
-      <c r="BH5">
-        <v>2.62</v>
-      </c>
-      <c r="BI5">
-        <v>2.28</v>
-      </c>
-      <c r="BJ5">
-        <v>12.5</v>
-      </c>
-      <c r="BK5">
-        <v>7.4</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>17.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.3</v>
-      </c>
-      <c r="BO5">
-        <v>3.9</v>
-      </c>
-      <c r="BP5">
-        <v>16.5</v>
-      </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU5">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW5">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA5">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6">
+        <v>1.86</v>
+      </c>
+      <c r="G6">
+        <v>2.14</v>
+      </c>
+      <c r="H6">
+        <v>4.3</v>
+      </c>
+      <c r="I6">
+        <v>6.4</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>4.4</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.12</v>
+      </c>
+      <c r="N6">
+        <v>2.56</v>
+      </c>
+      <c r="O6">
+        <v>1.52</v>
+      </c>
+      <c r="P6">
+        <v>1.48</v>
+      </c>
+      <c r="Q6">
+        <v>2.42</v>
+      </c>
+      <c r="R6">
+        <v>1.17</v>
+      </c>
+      <c r="S6">
+        <v>4.4</v>
+      </c>
+      <c r="T6">
+        <v>2.08</v>
+      </c>
+      <c r="U6">
+        <v>1.6</v>
+      </c>
+      <c r="V6">
+        <v>1.19</v>
+      </c>
+      <c r="W6">
+        <v>1.89</v>
+      </c>
+      <c r="X6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y6">
+        <v>15</v>
+      </c>
+      <c r="Z6">
+        <v>46</v>
+      </c>
+      <c r="AA6">
+        <v>190</v>
+      </c>
+      <c r="AB6">
+        <v>7.2</v>
+      </c>
+      <c r="AC6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>26</v>
+      </c>
+      <c r="AE6">
+        <v>120</v>
+      </c>
+      <c r="AF6">
+        <v>12</v>
+      </c>
+      <c r="AG6">
+        <v>13</v>
+      </c>
+      <c r="AH6">
+        <v>32</v>
+      </c>
+      <c r="AI6">
+        <v>150</v>
+      </c>
+      <c r="AJ6">
+        <v>29</v>
+      </c>
+      <c r="AK6">
+        <v>34</v>
+      </c>
+      <c r="AL6">
+        <v>75</v>
+      </c>
+      <c r="AM6">
+        <v>270</v>
+      </c>
+      <c r="AN6">
+        <v>30</v>
+      </c>
+      <c r="AO6">
+        <v>210</v>
+      </c>
+      <c r="AP6">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6">
+        <v>1.03</v>
+      </c>
+      <c r="AR6">
+        <v>1.03</v>
+      </c>
+      <c r="AS6">
+        <v>1.03</v>
+      </c>
+      <c r="AT6">
+        <v>1.03</v>
+      </c>
+      <c r="AU6">
+        <v>1.03</v>
+      </c>
+      <c r="AV6">
+        <v>1.03</v>
+      </c>
+      <c r="AW6">
+        <v>1.03</v>
+      </c>
+      <c r="AX6">
+        <v>1.03</v>
+      </c>
+      <c r="AY6">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6">
+        <v>1.03</v>
+      </c>
+      <c r="BA6">
+        <v>1.03</v>
+      </c>
+      <c r="BB6">
+        <v>1.03</v>
+      </c>
+      <c r="BC6">
+        <v>1.03</v>
+      </c>
+      <c r="BD6">
+        <v>1.03</v>
+      </c>
+      <c r="BE6">
+        <v>1.03</v>
+      </c>
+      <c r="BF6">
+        <v>19</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>2.98</v>
+      </c>
+      <c r="BI6">
+        <v>2.28</v>
+      </c>
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>4.8</v>
+      </c>
+      <c r="BO6">
+        <v>3.45</v>
+      </c>
+      <c r="BP6">
+        <v>18</v>
+      </c>
+      <c r="BQ6">
+        <v>12</v>
+      </c>
+      <c r="BR6">
+        <v>48</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU6">
+        <v>6.6</v>
+      </c>
+      <c r="BV6">
+        <v>70</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>95</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>50</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>2.64</v>
+      </c>
+      <c r="G7">
+        <v>3.05</v>
+      </c>
+      <c r="H7">
+        <v>2.76</v>
+      </c>
+      <c r="I7">
+        <v>4.1</v>
+      </c>
+      <c r="J7">
+        <v>2.48</v>
+      </c>
+      <c r="K7">
+        <v>3.9</v>
+      </c>
+      <c r="L7">
+        <v>1.61</v>
+      </c>
+      <c r="M7">
+        <v>1.12</v>
+      </c>
+      <c r="N7">
+        <v>2.36</v>
+      </c>
+      <c r="O7">
+        <v>1.58</v>
+      </c>
+      <c r="P7">
+        <v>1.45</v>
+      </c>
+      <c r="Q7">
+        <v>2.52</v>
+      </c>
+      <c r="R7">
+        <v>1.17</v>
+      </c>
+      <c r="S7">
+        <v>5.2</v>
+      </c>
+      <c r="T7">
+        <v>2.16</v>
+      </c>
+      <c r="U7">
+        <v>1.71</v>
+      </c>
+      <c r="V7">
+        <v>1.32</v>
+      </c>
+      <c r="W7">
+        <v>1.48</v>
+      </c>
+      <c r="X7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y7">
+        <v>9</v>
+      </c>
+      <c r="Z7">
+        <v>21</v>
+      </c>
+      <c r="AA7">
+        <v>80</v>
+      </c>
+      <c r="AB7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>7.4</v>
+      </c>
+      <c r="AD7">
+        <v>16</v>
+      </c>
+      <c r="AE7">
+        <v>65</v>
+      </c>
+      <c r="AF7">
+        <v>18</v>
+      </c>
+      <c r="AG7">
+        <v>20</v>
+      </c>
+      <c r="AH7">
+        <v>26</v>
+      </c>
+      <c r="AI7">
+        <v>110</v>
+      </c>
+      <c r="AJ7">
+        <v>65</v>
+      </c>
+      <c r="AK7">
+        <v>55</v>
+      </c>
+      <c r="AL7">
+        <v>95</v>
+      </c>
+      <c r="AM7">
+        <v>260</v>
+      </c>
+      <c r="AN7">
+        <v>70</v>
+      </c>
+      <c r="AO7">
+        <v>90</v>
+      </c>
+      <c r="AP7">
+        <v>5.8</v>
+      </c>
+      <c r="AQ7">
+        <v>7.4</v>
+      </c>
+      <c r="AR7">
+        <v>17</v>
+      </c>
+      <c r="AS7">
+        <v>1.03</v>
+      </c>
+      <c r="AT7">
+        <v>6.6</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>12.5</v>
+      </c>
+      <c r="AW7">
+        <v>1.03</v>
+      </c>
+      <c r="AX7">
+        <v>14</v>
+      </c>
+      <c r="AY7">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>1.03</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>1.03</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.03</v>
+      </c>
+      <c r="BF7">
+        <v>40</v>
+      </c>
+      <c r="BG7">
+        <v>50</v>
+      </c>
+      <c r="BH7">
+        <v>2.64</v>
+      </c>
+      <c r="BI7">
+        <v>2.12</v>
+      </c>
+      <c r="BJ7">
+        <v>12</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>5.8</v>
+      </c>
+      <c r="BO7">
+        <v>4.2</v>
+      </c>
+      <c r="BP7">
+        <v>28</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>6.4</v>
+      </c>
+      <c r="BU7">
+        <v>4.6</v>
+      </c>
+      <c r="BV7">
+        <v>34</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>65</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>1.12</v>
+      </c>
+      <c r="G8">
+        <v>440</v>
+      </c>
+      <c r="H8">
+        <v>1.11</v>
+      </c>
+      <c r="I8">
+        <v>970</v>
+      </c>
+      <c r="J8">
+        <v>1.12</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.26</v>
+      </c>
+      <c r="O8">
+        <v>1.4</v>
+      </c>
+      <c r="P8">
+        <v>1.25</v>
+      </c>
+      <c r="Q8">
+        <v>1.4</v>
+      </c>
+      <c r="R8">
+        <v>1.13</v>
+      </c>
+      <c r="S8">
+        <v>1.41</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.11</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>1.6</v>
+      </c>
+      <c r="G9">
+        <v>110</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>110</v>
+      </c>
+      <c r="J9">
+        <v>1.02</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.26</v>
+      </c>
+      <c r="O9">
+        <v>1.44</v>
+      </c>
+      <c r="P9">
+        <v>1.26</v>
+      </c>
+      <c r="Q9">
+        <v>2.24</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>3.75</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
         <v>81</v>
       </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10">
+        <v>1.94</v>
+      </c>
+      <c r="G10">
+        <v>2.02</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>5.5</v>
+      </c>
+      <c r="J10">
+        <v>3.15</v>
+      </c>
+      <c r="K10">
+        <v>3.35</v>
+      </c>
+      <c r="L10">
+        <v>1.62</v>
+      </c>
+      <c r="M10">
+        <v>1.13</v>
+      </c>
+      <c r="N10">
+        <v>2.46</v>
+      </c>
+      <c r="O10">
+        <v>1.61</v>
+      </c>
+      <c r="P10">
+        <v>1.48</v>
+      </c>
+      <c r="Q10">
+        <v>2.8</v>
+      </c>
+      <c r="R10">
+        <v>1.18</v>
+      </c>
+      <c r="S10">
+        <v>6</v>
+      </c>
+      <c r="T10">
+        <v>2.36</v>
+      </c>
+      <c r="U10">
+        <v>1.65</v>
+      </c>
+      <c r="V10">
+        <v>1.22</v>
+      </c>
+      <c r="W10">
+        <v>1.99</v>
+      </c>
+      <c r="X10">
+        <v>8</v>
+      </c>
+      <c r="Y10">
+        <v>12.5</v>
+      </c>
+      <c r="Z10">
+        <v>48</v>
+      </c>
+      <c r="AA10">
+        <v>210</v>
+      </c>
+      <c r="AB10">
+        <v>6.2</v>
+      </c>
+      <c r="AC10">
+        <v>7.8</v>
+      </c>
+      <c r="AD10">
+        <v>950</v>
+      </c>
+      <c r="AE10">
+        <v>140</v>
+      </c>
+      <c r="AF10">
+        <v>12.5</v>
+      </c>
+      <c r="AG10">
+        <v>12</v>
+      </c>
+      <c r="AH10">
+        <v>36</v>
+      </c>
+      <c r="AI10">
+        <v>160</v>
+      </c>
+      <c r="AJ10">
+        <v>30</v>
+      </c>
+      <c r="AK10">
+        <v>36</v>
+      </c>
+      <c r="AL10">
         <v>85</v>
       </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6">
-        <v>1.31</v>
-      </c>
-      <c r="G6">
+      <c r="AM10">
+        <v>320</v>
+      </c>
+      <c r="AN10">
+        <v>34</v>
+      </c>
+      <c r="AO10">
+        <v>250</v>
+      </c>
+      <c r="AP10">
+        <v>7.2</v>
+      </c>
+      <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
+        <v>6.8</v>
+      </c>
+      <c r="AS10">
+        <v>7.8</v>
+      </c>
+      <c r="AT10">
+        <v>5.5</v>
+      </c>
+      <c r="AU10">
+        <v>6.8</v>
+      </c>
+      <c r="AV10">
+        <v>17</v>
+      </c>
+      <c r="AW10">
+        <v>7.6</v>
+      </c>
+      <c r="AX10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>6.6</v>
+      </c>
+      <c r="BA10">
+        <v>7.6</v>
+      </c>
+      <c r="BB10">
+        <v>21</v>
+      </c>
+      <c r="BC10">
+        <v>6.6</v>
+      </c>
+      <c r="BD10">
+        <v>7.4</v>
+      </c>
+      <c r="BE10">
+        <v>7.8</v>
+      </c>
+      <c r="BF10">
+        <v>19.5</v>
+      </c>
+      <c r="BG10">
+        <v>7.8</v>
+      </c>
+      <c r="BH10">
+        <v>2.6</v>
+      </c>
+      <c r="BI10">
+        <v>2.28</v>
+      </c>
+      <c r="BJ10">
+        <v>12.5</v>
+      </c>
+      <c r="BK10">
+        <v>7.6</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>2.28</v>
+      </c>
+      <c r="BN10">
+        <v>4.3</v>
+      </c>
+      <c r="BO10">
+        <v>3.9</v>
+      </c>
+      <c r="BP10">
+        <v>16.5</v>
+      </c>
+      <c r="BQ10">
+        <v>9</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>13.5</v>
+      </c>
+      <c r="BT10">
+        <v>8.6</v>
+      </c>
+      <c r="BU10">
+        <v>6</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>2.2</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>16</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>14</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11">
+        <v>1.32</v>
+      </c>
+      <c r="G11">
         <v>1.35</v>
       </c>
-      <c r="H6">
+      <c r="H11">
         <v>12.5</v>
       </c>
-      <c r="I6">
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>5.4</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11">
+        <v>1.4</v>
+      </c>
+      <c r="M11">
+        <v>1.07</v>
+      </c>
+      <c r="N11">
+        <v>3.55</v>
+      </c>
+      <c r="O11">
+        <v>1.34</v>
+      </c>
+      <c r="P11">
+        <v>1.88</v>
+      </c>
+      <c r="Q11">
+        <v>1.98</v>
+      </c>
+      <c r="R11">
+        <v>1.33</v>
+      </c>
+      <c r="S11">
+        <v>3.6</v>
+      </c>
+      <c r="T11">
+        <v>2.62</v>
+      </c>
+      <c r="U11">
+        <v>1.53</v>
+      </c>
+      <c r="V11">
+        <v>1.06</v>
+      </c>
+      <c r="W11">
+        <v>3.85</v>
+      </c>
+      <c r="X11">
+        <v>18.5</v>
+      </c>
+      <c r="Y11">
+        <v>38</v>
+      </c>
+      <c r="Z11">
+        <v>170</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>6.6</v>
+      </c>
+      <c r="AC11">
+        <v>13.5</v>
+      </c>
+      <c r="AD11">
+        <v>60</v>
+      </c>
+      <c r="AE11">
+        <v>420</v>
+      </c>
+      <c r="AF11">
+        <v>6.8</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>55</v>
+      </c>
+      <c r="AI11">
+        <v>320</v>
+      </c>
+      <c r="AJ11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK11">
+        <v>18</v>
+      </c>
+      <c r="AL11">
+        <v>65</v>
+      </c>
+      <c r="AM11">
+        <v>450</v>
+      </c>
+      <c r="AN11">
+        <v>7.2</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>13.5</v>
+      </c>
+      <c r="AQ11">
+        <v>7.8</v>
+      </c>
+      <c r="AR11">
+        <v>9.4</v>
+      </c>
+      <c r="AS11">
+        <v>10</v>
+      </c>
+      <c r="AT11">
+        <v>5.7</v>
+      </c>
+      <c r="AU11">
+        <v>11.5</v>
+      </c>
+      <c r="AV11">
+        <v>8.4</v>
+      </c>
+      <c r="AW11">
+        <v>9.6</v>
+      </c>
+      <c r="AX11">
+        <v>5.9</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>8.4</v>
+      </c>
+      <c r="BA11">
+        <v>9.6</v>
+      </c>
+      <c r="BB11">
+        <v>8.6</v>
+      </c>
+      <c r="BC11">
         <v>15.5</v>
       </c>
-      <c r="J6">
-        <v>5.4</v>
-      </c>
-      <c r="K6">
+      <c r="BD11">
+        <v>8.6</v>
+      </c>
+      <c r="BE11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF11">
         <v>6.2</v>
       </c>
-      <c r="L6">
-        <v>1.4</v>
-      </c>
-      <c r="M6">
-        <v>1.07</v>
-      </c>
-      <c r="N6">
-        <v>3.55</v>
-      </c>
-      <c r="O6">
-        <v>1.34</v>
-      </c>
-      <c r="P6">
-        <v>1.88</v>
-      </c>
-      <c r="Q6">
-        <v>1.98</v>
-      </c>
-      <c r="R6">
-        <v>1.33</v>
-      </c>
-      <c r="S6">
-        <v>3.6</v>
-      </c>
-      <c r="T6">
-        <v>2.62</v>
-      </c>
-      <c r="U6">
-        <v>1.53</v>
-      </c>
-      <c r="V6">
-        <v>1.06</v>
-      </c>
-      <c r="W6">
-        <v>3.85</v>
-      </c>
-      <c r="X6">
-        <v>18.5</v>
-      </c>
-      <c r="Y6">
-        <v>38</v>
-      </c>
-      <c r="Z6">
-        <v>170</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>6.6</v>
-      </c>
-      <c r="AC6">
-        <v>13.5</v>
-      </c>
-      <c r="AD6">
-        <v>60</v>
-      </c>
-      <c r="AE6">
-        <v>420</v>
-      </c>
-      <c r="AF6">
-        <v>6.8</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>55</v>
-      </c>
-      <c r="AI6">
-        <v>320</v>
-      </c>
-      <c r="AJ6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK6">
-        <v>18</v>
-      </c>
-      <c r="AL6">
-        <v>65</v>
-      </c>
-      <c r="AM6">
-        <v>450</v>
-      </c>
-      <c r="AN6">
-        <v>7.2</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>13.5</v>
-      </c>
-      <c r="AQ6">
+      <c r="BG11">
+        <v>10</v>
+      </c>
+      <c r="BH11">
+        <v>3.5</v>
+      </c>
+      <c r="BI11">
+        <v>2.88</v>
+      </c>
+      <c r="BJ11">
+        <v>15.5</v>
+      </c>
+      <c r="BK11">
+        <v>8</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>15.5</v>
+      </c>
+      <c r="BN11">
+        <v>3.4</v>
+      </c>
+      <c r="BO11">
+        <v>2.82</v>
+      </c>
+      <c r="BP11">
         <v>7.8</v>
       </c>
-      <c r="AR6">
-        <v>9.4</v>
-      </c>
-      <c r="AS6">
-        <v>10</v>
-      </c>
-      <c r="AT6">
-        <v>5.7</v>
-      </c>
-      <c r="AU6">
-        <v>11.5</v>
-      </c>
-      <c r="AV6">
+      <c r="BQ11">
+        <v>5.8</v>
+      </c>
+      <c r="BR11">
+        <v>32</v>
+      </c>
+      <c r="BS11">
+        <v>10.5</v>
+      </c>
+      <c r="BT11">
+        <v>17</v>
+      </c>
+      <c r="BU11">
         <v>8.4</v>
       </c>
-      <c r="AW6">
-        <v>9.6</v>
-      </c>
-      <c r="AX6">
-        <v>5.9</v>
-      </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>8.4</v>
-      </c>
-      <c r="BA6">
-        <v>9.6</v>
-      </c>
-      <c r="BB6">
-        <v>8.6</v>
-      </c>
-      <c r="BC6">
-        <v>15.5</v>
-      </c>
-      <c r="BD6">
-        <v>8.6</v>
-      </c>
-      <c r="BE6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF6">
-        <v>6.2</v>
-      </c>
-      <c r="BG6">
-        <v>10</v>
-      </c>
-      <c r="BH6">
-        <v>3.5</v>
-      </c>
-      <c r="BI6">
-        <v>2.9</v>
-      </c>
-      <c r="BJ6">
-        <v>15.5</v>
-      </c>
-      <c r="BK6">
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>15</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>15</v>
+      </c>
+      <c r="BZ11">
+        <v>16</v>
+      </c>
+      <c r="CA11">
         <v>8</v>
       </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>16</v>
-      </c>
-      <c r="BN6">
-        <v>3.4</v>
-      </c>
-      <c r="BO6">
-        <v>2.82</v>
-      </c>
-      <c r="BP6">
-        <v>7.8</v>
-      </c>
-      <c r="BQ6">
-        <v>5.8</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>11</v>
-      </c>
-      <c r="BT6">
-        <v>17</v>
-      </c>
-      <c r="BU6">
-        <v>8.4</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>15</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>15</v>
-      </c>
-      <c r="BZ6">
-        <v>16</v>
-      </c>
-      <c r="CA6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>96</v>
+      <c r="CB11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12">
+        <v>1.45</v>
+      </c>
+      <c r="G12">
+        <v>4.4</v>
+      </c>
+      <c r="H12">
+        <v>2.3</v>
+      </c>
+      <c r="I12">
+        <v>160</v>
+      </c>
+      <c r="J12">
+        <v>2.98</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.26</v>
+      </c>
+      <c r="O12">
+        <v>1.42</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.42</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>1.43</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.29</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12">
+        <v>1.03</v>
+      </c>
+      <c r="AR12">
+        <v>1.03</v>
+      </c>
+      <c r="AS12">
+        <v>1.03</v>
+      </c>
+      <c r="AT12">
+        <v>1.03</v>
+      </c>
+      <c r="AU12">
+        <v>1.03</v>
+      </c>
+      <c r="AV12">
+        <v>1.03</v>
+      </c>
+      <c r="AW12">
+        <v>1.03</v>
+      </c>
+      <c r="AX12">
+        <v>1.03</v>
+      </c>
+      <c r="AY12">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12">
+        <v>1.03</v>
+      </c>
+      <c r="BA12">
+        <v>1.03</v>
+      </c>
+      <c r="BB12">
+        <v>1.03</v>
+      </c>
+      <c r="BC12">
+        <v>1.03</v>
+      </c>
+      <c r="BD12">
+        <v>1.03</v>
+      </c>
+      <c r="BE12">
+        <v>1.03</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -352,7 +352,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 09:48:01</t>
+    <t>2026-08-11 11:55:15</t>
   </si>
 </sst>
 </file>
@@ -949,19 +949,19 @@
         <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.63</v>
@@ -976,13 +976,13 @@
         <v>1.61</v>
       </c>
       <c r="P2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q2">
         <v>2.86</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
         <v>6.2</v>
@@ -991,10 +991,10 @@
         <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.64</v>
@@ -1003,7 +1003,7 @@
         <v>7.8</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z2">
         <v>23</v>
@@ -1021,10 +1021,10 @@
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
         <v>38</v>
@@ -1042,37 +1042,37 @@
         <v>38</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS2">
         <v>55</v>
       </c>
       <c r="AT2">
+        <v>6.8</v>
+      </c>
+      <c r="AU2">
         <v>6.6</v>
       </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW2">
         <v>50</v>
@@ -1081,49 +1081,49 @@
         <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
         <v>23</v>
       </c>
       <c r="BA2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE2">
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BG2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
@@ -1132,16 +1132,16 @@
         <v>4.6</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>6.4</v>
@@ -1153,19 +1153,19 @@
         <v>40</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>70</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1212,28 +1212,28 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
         <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
         <v>1.56</v>
@@ -1257,7 +1257,7 @@
         <v>17</v>
       </c>
       <c r="AC3">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
         <v>950</v>
@@ -1296,58 +1296,58 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AQ3">
         <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AS3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AT3">
-        <v>1.95</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>6</v>
       </c>
       <c r="AV3">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AW3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AX3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AY3">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BA3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BB3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BC3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BD3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BE3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BF3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BG3">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1430,7 +1430,7 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G4">
         <v>1.77</v>
@@ -1439,46 +1439,46 @@
         <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
+        <v>1.57</v>
+      </c>
+      <c r="M4">
+        <v>1.12</v>
+      </c>
+      <c r="N4">
+        <v>2.74</v>
+      </c>
+      <c r="O4">
+        <v>1.55</v>
+      </c>
+      <c r="P4">
         <v>1.56</v>
       </c>
-      <c r="M4">
-        <v>1.11</v>
-      </c>
-      <c r="N4">
-        <v>2.82</v>
-      </c>
-      <c r="O4">
-        <v>1.53</v>
-      </c>
-      <c r="P4">
-        <v>1.6</v>
-      </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
         <v>2.28</v>
@@ -1490,19 +1490,19 @@
         <v>15.5</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA4">
         <v>240</v>
       </c>
       <c r="AB4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE4">
         <v>140</v>
@@ -1538,16 +1538,16 @@
         <v>260</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>5.4</v>
@@ -1556,10 +1556,10 @@
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX4">
         <v>7.8</v>
@@ -1568,46 +1568,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB4">
         <v>16</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD4">
         <v>17</v>
       </c>
       <c r="BE4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BI4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>4.1</v>
@@ -1619,37 +1619,37 @@
         <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT4">
         <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,226 +1672,226 @@
         <v>104</v>
       </c>
       <c r="F5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
         <v>1.53</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="O5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P5">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Q5">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R5">
         <v>1.16</v>
       </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="T5">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
         <v>1.38</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>16</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH5">
         <v>2.68</v>
       </c>
       <c r="BI5">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BN5">
         <v>6.4</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP5">
         <v>34</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BT5">
         <v>5.7</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV5">
         <v>27</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BX5">
         <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ5">
         <v>60</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1917,67 +1917,67 @@
         <v>1.86</v>
       </c>
       <c r="G6">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M6">
         <v>1.12</v>
       </c>
       <c r="N6">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="X6">
         <v>9.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA6">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB6">
         <v>7.2</v>
@@ -1986,10 +1986,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF6">
         <v>12</v>
@@ -2004,10 +2004,10 @@
         <v>150</v>
       </c>
       <c r="AJ6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6">
         <v>75</v>
@@ -2016,64 +2016,64 @@
         <v>270</v>
       </c>
       <c r="AN6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO6">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2085,55 +2085,55 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="BP6">
         <v>18</v>
       </c>
       <c r="BQ6">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT6">
         <v>9.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="BV6">
         <v>70</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX6">
         <v>95</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ6">
         <v>50</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB6" t="s">
         <v>112</v>
@@ -2156,25 +2156,25 @@
         <v>106</v>
       </c>
       <c r="F7">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3.5</v>
+      </c>
+      <c r="J7">
         <v>2.76</v>
       </c>
-      <c r="I7">
-        <v>4.1</v>
-      </c>
-      <c r="J7">
-        <v>2.48</v>
-      </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="M7">
         <v>1.12</v>
@@ -2189,64 +2189,64 @@
         <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="R7">
         <v>1.17</v>
       </c>
       <c r="S7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
         <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
         <v>9.199999999999999</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA7">
         <v>80</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>65</v>
       </c>
       <c r="AF7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI7">
         <v>110</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2273,19 +2273,19 @@
         <v>17</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
         <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AV7">
         <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
         <v>14</v>
@@ -2297,25 +2297,25 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
         <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>2.64</v>
@@ -2327,13 +2327,13 @@
         <v>12</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN7">
         <v>5.8</v>
@@ -2345,13 +2345,13 @@
         <v>28</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
         <v>6.4</v>
@@ -2363,19 +2363,19 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7">
         <v>65</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="s">
         <v>112</v>
@@ -2398,139 +2398,139 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="G8">
-        <v>440</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="I8">
-        <v>970</v>
+        <v>1.67</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="O8">
         <v>1.4</v>
       </c>
       <c r="P8">
+        <v>1.67</v>
+      </c>
+      <c r="Q8">
+        <v>2.2</v>
+      </c>
+      <c r="R8">
         <v>1.25</v>
       </c>
-      <c r="Q8">
-        <v>1.4</v>
-      </c>
-      <c r="R8">
-        <v>1.13</v>
-      </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V8">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
         <v>1.03</v>
@@ -2539,85 +2539,85 @@
         <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2640,19 +2640,19 @@
         <v>108</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>6.6</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2667,19 +2667,19 @@
         <v>1.26</v>
       </c>
       <c r="O9">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>3.75</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2688,10 +2688,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2912,7 +2912,7 @@
         <v>1.61</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q10">
         <v>2.8</v>
@@ -3124,22 +3124,22 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H11">
         <v>12.5</v>
       </c>
       <c r="I11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
         <v>1.4</v>
@@ -3148,7 +3148,7 @@
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
         <v>1.34</v>
@@ -3181,7 +3181,7 @@
         <v>18.5</v>
       </c>
       <c r="Y11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z11">
         <v>170</v>
@@ -3193,7 +3193,7 @@
         <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD11">
         <v>60</v>
@@ -3235,13 +3235,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11">
         <v>5.7</v>
@@ -3262,7 +3262,7 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA11">
         <v>9.6</v>
@@ -3277,13 +3277,13 @@
         <v>8.6</v>
       </c>
       <c r="BE11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF11">
         <v>6.2</v>
       </c>
       <c r="BG11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11">
         <v>3.5</v>
@@ -3366,13 +3366,13 @@
         <v>111</v>
       </c>
       <c r="F12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H12">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I12">
         <v>160</v>
@@ -3393,19 +3393,19 @@
         <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P12">
         <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3414,10 +3414,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X12">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>Argentinian Torneo A</t>
+  </si>
+  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
@@ -277,9 +280,18 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -289,12 +301,12 @@
     <t>Talleres</t>
   </si>
   <si>
-    <t>Tolima</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
+    <t>FADEP Mendoza</t>
+  </si>
+  <si>
     <t>Milford</t>
   </si>
   <si>
@@ -307,6 +319,12 @@
     <t>AmaZulu</t>
   </si>
   <si>
+    <t>CA Germinal</t>
+  </si>
+  <si>
+    <t>Independiente Chivilcoy</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
@@ -322,12 +340,12 @@
     <t>Lanus</t>
   </si>
   <si>
-    <t>Independiente (Ecu)</t>
-  </si>
-  <si>
     <t>Univ Catolica (Chile)</t>
   </si>
   <si>
+    <t>CA Costa Brava</t>
+  </si>
+  <si>
     <t>Siwelele FC</t>
   </si>
   <si>
@@ -340,6 +358,12 @@
     <t>Orlando Pirates (SA)</t>
   </si>
   <si>
+    <t>Santamarina</t>
+  </si>
+  <si>
+    <t>Sarmiento de Resistencia</t>
+  </si>
+  <si>
     <t>Cobreloa Calama</t>
   </si>
   <si>
@@ -352,7 +376,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 11:55:15</t>
+    <t>2026-08-11 14:02:40</t>
   </si>
 </sst>
 </file>
@@ -684,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,16 +958,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F2">
         <v>2.5</v>
@@ -961,37 +985,37 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T2">
         <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -1012,7 +1036,7 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>7</v>
@@ -1021,49 +1045,49 @@
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2">
         <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO2">
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1099,10 +1123,10 @@
         <v>60</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG2">
         <v>36</v>
@@ -1117,49 +1141,49 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2">
         <v>11</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>60</v>
@@ -1168,7 +1192,7 @@
         <v>12.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,515 +1200,515 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>1.74</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>1.76</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="X3">
+        <v>9.6</v>
+      </c>
+      <c r="Y3">
+        <v>16.5</v>
+      </c>
+      <c r="Z3">
+        <v>60</v>
+      </c>
+      <c r="AA3">
+        <v>260</v>
+      </c>
+      <c r="AB3">
+        <v>6</v>
+      </c>
+      <c r="AC3">
+        <v>8.6</v>
+      </c>
+      <c r="AD3">
+        <v>32</v>
+      </c>
+      <c r="AE3">
+        <v>160</v>
+      </c>
+      <c r="AF3">
+        <v>8.6</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
+        <v>34</v>
+      </c>
+      <c r="AI3">
+        <v>160</v>
+      </c>
+      <c r="AJ3">
+        <v>20</v>
+      </c>
+      <c r="AK3">
+        <v>26</v>
+      </c>
+      <c r="AL3">
+        <v>95</v>
+      </c>
+      <c r="AM3">
+        <v>300</v>
+      </c>
+      <c r="AN3">
+        <v>21</v>
+      </c>
+      <c r="AO3">
+        <v>290</v>
+      </c>
+      <c r="AP3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>13.5</v>
+      </c>
+      <c r="AR3">
+        <v>42</v>
+      </c>
+      <c r="AS3">
+        <v>9.4</v>
+      </c>
+      <c r="AT3">
+        <v>5.4</v>
+      </c>
+      <c r="AU3">
+        <v>7.4</v>
+      </c>
+      <c r="AV3">
+        <v>23</v>
+      </c>
+      <c r="AW3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX3">
+        <v>7.6</v>
+      </c>
+      <c r="AY3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>26</v>
+      </c>
+      <c r="BA3">
+        <v>9.4</v>
+      </c>
+      <c r="BB3">
+        <v>16</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
+        <v>22</v>
+      </c>
+      <c r="BE3">
+        <v>9.4</v>
+      </c>
+      <c r="BF3">
+        <v>15</v>
+      </c>
+      <c r="BG3">
+        <v>9.4</v>
+      </c>
+      <c r="BH3">
+        <v>2.86</v>
+      </c>
+      <c r="BI3">
+        <v>2.5</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>9</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>10.5</v>
       </c>
-      <c r="Y3">
-        <v>14.5</v>
-      </c>
-      <c r="Z3">
-        <v>23</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>17</v>
-      </c>
-      <c r="AC3">
+      <c r="BN3">
+        <v>4.1</v>
+      </c>
+      <c r="BO3">
+        <v>3.45</v>
+      </c>
+      <c r="BP3">
+        <v>14</v>
+      </c>
+      <c r="BQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT3">
         <v>10.5</v>
       </c>
-      <c r="AD3">
-        <v>950</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>30</v>
-      </c>
-      <c r="AG3">
-        <v>950</v>
-      </c>
-      <c r="AH3">
-        <v>950</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.78</v>
-      </c>
-      <c r="AQ3">
-        <v>7.2</v>
-      </c>
-      <c r="AR3">
-        <v>1.96</v>
-      </c>
-      <c r="AS3">
-        <v>2.14</v>
-      </c>
-      <c r="AT3">
-        <v>8.4</v>
-      </c>
-      <c r="AU3">
-        <v>6</v>
-      </c>
-      <c r="AV3">
-        <v>1.93</v>
-      </c>
-      <c r="AW3">
-        <v>2.14</v>
-      </c>
-      <c r="AX3">
-        <v>2</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>2.02</v>
-      </c>
-      <c r="BA3">
-        <v>2.14</v>
-      </c>
-      <c r="BB3">
-        <v>2.14</v>
-      </c>
-      <c r="BC3">
-        <v>2.14</v>
-      </c>
-      <c r="BD3">
-        <v>2.14</v>
-      </c>
-      <c r="BE3">
-        <v>2.14</v>
-      </c>
-      <c r="BF3">
-        <v>2.14</v>
-      </c>
-      <c r="BG3">
-        <v>2.14</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>1.75</v>
+        <v>1.02</v>
       </c>
       <c r="G4">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.26</v>
+      </c>
+      <c r="O4">
+        <v>1.59</v>
+      </c>
+      <c r="P4">
+        <v>1.25</v>
+      </c>
+      <c r="Q4">
+        <v>1.59</v>
+      </c>
+      <c r="R4">
         <v>1.12</v>
       </c>
-      <c r="N4">
-        <v>2.74</v>
-      </c>
-      <c r="O4">
-        <v>1.55</v>
-      </c>
-      <c r="P4">
-        <v>1.56</v>
-      </c>
-      <c r="Q4">
-        <v>2.72</v>
-      </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
       <c r="S4">
-        <v>5.6</v>
+        <v>1.59</v>
       </c>
       <c r="T4">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H5">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K5">
         <v>3.15</v>
@@ -1693,19 +1717,19 @@
         <v>1.53</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
         <v>2.46</v>
       </c>
       <c r="O5">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
         <v>1.47</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="R5">
         <v>1.16</v>
@@ -1714,16 +1738,16 @@
         <v>5.2</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="X5">
         <v>9.199999999999999</v>
@@ -1759,7 +1783,7 @@
         <v>28</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>75</v>
@@ -1768,13 +1792,13 @@
         <v>65</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>240</v>
       </c>
       <c r="AN5">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1786,13 +1810,13 @@
         <v>6.2</v>
       </c>
       <c r="AR5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU5">
         <v>5.5</v>
@@ -1804,19 +1828,19 @@
         <v>4.7</v>
       </c>
       <c r="AX5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY5">
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC5">
         <v>4.8</v>
@@ -1825,10 +1849,10 @@
         <v>4.9</v>
       </c>
       <c r="BE5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG5">
         <v>4.8</v>
@@ -1837,7 +1861,7 @@
         <v>2.68</v>
       </c>
       <c r="BI5">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5">
         <v>12</v>
@@ -1849,75 +1873,75 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>6.4</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
         <v>34</v>
       </c>
       <c r="BQ5">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="BR5">
         <v>60</v>
       </c>
       <c r="BS5">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>5.7</v>
       </c>
       <c r="BU5">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV5">
         <v>27</v>
       </c>
       <c r="BW5">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
         <v>55</v>
       </c>
       <c r="BY5">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>60</v>
       </c>
       <c r="CA5">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F6">
         <v>1.86</v>
       </c>
       <c r="G6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H6">
         <v>4.9</v>
@@ -1926,46 +1950,46 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
         <v>1.12</v>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O6">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.59</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X6">
         <v>9.800000000000001</v>
@@ -2040,7 +2064,7 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
         <v>5.1</v>
@@ -2061,7 +2085,7 @@
         <v>18</v>
       </c>
       <c r="BC6">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BD6">
         <v>4.9</v>
@@ -2097,7 +2121,7 @@
         <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="BP6">
         <v>18</v>
@@ -2106,10 +2130,10 @@
         <v>4.6</v>
       </c>
       <c r="BR6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
         <v>9.800000000000001</v>
@@ -2124,7 +2148,7 @@
         <v>5.7</v>
       </c>
       <c r="BX6">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>5.8</v>
@@ -2136,30 +2160,30 @@
         <v>5.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -2174,10 +2198,10 @@
         <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
         <v>2.36</v>
@@ -2195,10 +2219,10 @@
         <v>1.17</v>
       </c>
       <c r="S7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U7">
         <v>1.71</v>
@@ -2207,40 +2231,40 @@
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X7">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB7">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI7">
         <v>110</v>
@@ -2249,52 +2273,52 @@
         <v>55</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM7">
         <v>260</v>
       </c>
       <c r="AN7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP7">
         <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS7">
         <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU7">
         <v>5.3</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
         <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BA7">
         <v>1.01</v>
@@ -2303,7 +2327,7 @@
         <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
         <v>1.01</v>
@@ -2321,7 +2345,7 @@
         <v>2.64</v>
       </c>
       <c r="BI7">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2378,30 +2402,30 @@
         <v>9.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F8">
         <v>7.2</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8">
         <v>1.56</v>
@@ -2416,13 +2440,13 @@
         <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O8">
         <v>1.4</v>
@@ -2440,13 +2464,13 @@
         <v>4.1</v>
       </c>
       <c r="T8">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="U8">
         <v>1.6</v>
       </c>
       <c r="V8">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="W8">
         <v>1.12</v>
@@ -2455,13 +2479,13 @@
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z8">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA8">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AB8">
         <v>23</v>
@@ -2509,16 +2533,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR8">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS8">
         <v>11.5</v>
       </c>
       <c r="AT8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2527,7 +2551,7 @@
         <v>8</v>
       </c>
       <c r="AW8">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX8">
         <v>1.01</v>
@@ -2599,7 +2623,7 @@
         <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="BV8">
         <v>12.5</v>
@@ -2620,42 +2644,42 @@
         <v>5.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="G9">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="I9">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2664,23 +2688,23 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.12</v>
+      </c>
+      <c r="S9">
         <v>1.02</v>
       </c>
-      <c r="P9">
-        <v>1.25</v>
-      </c>
-      <c r="Q9">
-        <v>1.45</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>1.49</v>
-      </c>
       <c r="T9">
         <v>1.01</v>
       </c>
@@ -2688,10 +2712,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2748,52 +2772,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2856,739 +2880,1223 @@
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>1.94</v>
+        <v>1.02</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K10">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L10">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S10">
-        <v>6</v>
+        <v>1.48</v>
       </c>
       <c r="T10">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>1.31</v>
+        <v>2.48</v>
       </c>
       <c r="G11">
-        <v>1.34</v>
+        <v>2.86</v>
       </c>
       <c r="H11">
-        <v>12.5</v>
+        <v>2.76</v>
       </c>
       <c r="I11">
-        <v>15.5</v>
+        <v>3.25</v>
       </c>
       <c r="J11">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T11">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
+        <v>2.06</v>
+      </c>
+      <c r="V11">
+        <v>1.45</v>
+      </c>
+      <c r="W11">
         <v>1.53</v>
       </c>
-      <c r="V11">
-        <v>1.06</v>
-      </c>
-      <c r="W11">
-        <v>3.85</v>
-      </c>
       <c r="X11">
+        <v>15.5</v>
+      </c>
+      <c r="Y11">
+        <v>12</v>
+      </c>
+      <c r="Z11">
+        <v>21</v>
+      </c>
+      <c r="AA11">
+        <v>55</v>
+      </c>
+      <c r="AB11">
+        <v>11.5</v>
+      </c>
+      <c r="AC11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11">
+        <v>38</v>
+      </c>
+      <c r="AF11">
         <v>18.5</v>
       </c>
-      <c r="Y11">
-        <v>36</v>
-      </c>
-      <c r="Z11">
-        <v>170</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>18.5</v>
+      </c>
+      <c r="AI11">
+        <v>50</v>
+      </c>
+      <c r="AJ11">
+        <v>42</v>
+      </c>
+      <c r="AK11">
+        <v>32</v>
+      </c>
+      <c r="AL11">
+        <v>46</v>
+      </c>
+      <c r="AM11">
+        <v>120</v>
+      </c>
+      <c r="AN11">
+        <v>28</v>
+      </c>
+      <c r="AO11">
+        <v>34</v>
+      </c>
+      <c r="AP11">
+        <v>10</v>
+      </c>
+      <c r="AQ11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR11">
+        <v>15</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11">
         <v>6.6</v>
       </c>
-      <c r="AC11">
-        <v>14</v>
-      </c>
-      <c r="AD11">
-        <v>60</v>
-      </c>
-      <c r="AE11">
-        <v>420</v>
-      </c>
-      <c r="AF11">
-        <v>6.8</v>
-      </c>
-      <c r="AG11">
-        <v>11.5</v>
-      </c>
-      <c r="AH11">
-        <v>55</v>
-      </c>
-      <c r="AI11">
-        <v>320</v>
-      </c>
-      <c r="AJ11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK11">
-        <v>18</v>
-      </c>
-      <c r="AL11">
-        <v>65</v>
-      </c>
-      <c r="AM11">
-        <v>450</v>
-      </c>
-      <c r="AN11">
-        <v>7.2</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
+      <c r="AV11">
+        <v>11</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
         <v>13.5</v>
-      </c>
-      <c r="AQ11">
-        <v>7.6</v>
-      </c>
-      <c r="AR11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT11">
-        <v>5.7</v>
-      </c>
-      <c r="AU11">
-        <v>11.5</v>
-      </c>
-      <c r="AV11">
-        <v>8.4</v>
-      </c>
-      <c r="AW11">
-        <v>9.6</v>
-      </c>
-      <c r="AX11">
-        <v>5.9</v>
       </c>
       <c r="AY11">
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="BD11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BG11">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI11">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BK11">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
+        <v>36</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>6.4</v>
+      </c>
+      <c r="BU11">
+        <v>4.8</v>
+      </c>
+      <c r="BV11">
+        <v>25</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>38</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
         <v>32</v>
       </c>
-      <c r="BS11">
-        <v>10.5</v>
-      </c>
-      <c r="BT11">
-        <v>17</v>
-      </c>
-      <c r="BU11">
-        <v>8.4</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>15</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>15</v>
-      </c>
-      <c r="BZ11">
-        <v>16</v>
-      </c>
       <c r="CA11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="G12">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>160</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N12">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="O12">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>1.39</v>
+        <v>2.78</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V12">
+        <v>1.23</v>
+      </c>
+      <c r="W12">
+        <v>1.95</v>
+      </c>
+      <c r="X12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>46</v>
+      </c>
+      <c r="AA12">
+        <v>190</v>
+      </c>
+      <c r="AB12">
+        <v>6.2</v>
+      </c>
+      <c r="AC12">
+        <v>7.8</v>
+      </c>
+      <c r="AD12">
+        <v>950</v>
+      </c>
+      <c r="AE12">
+        <v>130</v>
+      </c>
+      <c r="AF12">
+        <v>13</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>36</v>
+      </c>
+      <c r="AI12">
+        <v>160</v>
+      </c>
+      <c r="AJ12">
+        <v>32</v>
+      </c>
+      <c r="AK12">
+        <v>30</v>
+      </c>
+      <c r="AL12">
+        <v>85</v>
+      </c>
+      <c r="AM12">
+        <v>320</v>
+      </c>
+      <c r="AN12">
+        <v>36</v>
+      </c>
+      <c r="AO12">
+        <v>230</v>
+      </c>
+      <c r="AP12">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12">
+        <v>10.5</v>
+      </c>
+      <c r="AR12">
+        <v>7</v>
+      </c>
+      <c r="AS12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT12">
+        <v>5.6</v>
+      </c>
+      <c r="AU12">
+        <v>6.8</v>
+      </c>
+      <c r="AV12">
+        <v>6</v>
+      </c>
+      <c r="AW12">
+        <v>8</v>
+      </c>
+      <c r="AX12">
+        <v>9.4</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>6.8</v>
+      </c>
+      <c r="BA12">
+        <v>8</v>
+      </c>
+      <c r="BB12">
+        <v>18.5</v>
+      </c>
+      <c r="BC12">
+        <v>6.6</v>
+      </c>
+      <c r="BD12">
+        <v>7.8</v>
+      </c>
+      <c r="BE12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>20</v>
+      </c>
+      <c r="BG12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12">
+        <v>2.62</v>
+      </c>
+      <c r="BI12">
+        <v>2.26</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>7.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>16</v>
+      </c>
+      <c r="BN12">
+        <v>4.4</v>
+      </c>
+      <c r="BO12">
+        <v>3.95</v>
+      </c>
+      <c r="BP12">
+        <v>17</v>
+      </c>
+      <c r="BQ12">
+        <v>8.6</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>12</v>
+      </c>
+      <c r="BT12">
+        <v>8.4</v>
+      </c>
+      <c r="BU12">
+        <v>5.6</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>13.5</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>14</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>12.5</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13">
+        <v>1.3</v>
+      </c>
+      <c r="G13">
+        <v>1.35</v>
+      </c>
+      <c r="H13">
+        <v>12.5</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>5.5</v>
+      </c>
+      <c r="K13">
+        <v>6.2</v>
+      </c>
+      <c r="L13">
+        <v>1.41</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>3.45</v>
+      </c>
+      <c r="O13">
+        <v>1.35</v>
+      </c>
+      <c r="P13">
+        <v>1.85</v>
+      </c>
+      <c r="Q13">
+        <v>2.02</v>
+      </c>
+      <c r="R13">
+        <v>1.31</v>
+      </c>
+      <c r="S13">
+        <v>3.7</v>
+      </c>
+      <c r="T13">
+        <v>2.68</v>
+      </c>
+      <c r="U13">
+        <v>1.51</v>
+      </c>
+      <c r="V13">
+        <v>1.07</v>
+      </c>
+      <c r="W13">
+        <v>3.85</v>
+      </c>
+      <c r="X13">
+        <v>18.5</v>
+      </c>
+      <c r="Y13">
+        <v>34</v>
+      </c>
+      <c r="Z13">
+        <v>170</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>6.4</v>
+      </c>
+      <c r="AC13">
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <v>60</v>
+      </c>
+      <c r="AE13">
+        <v>450</v>
+      </c>
+      <c r="AF13">
+        <v>7.8</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>60</v>
+      </c>
+      <c r="AI13">
+        <v>350</v>
+      </c>
+      <c r="AJ13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>80</v>
+      </c>
+      <c r="AM13">
+        <v>520</v>
+      </c>
+      <c r="AN13">
+        <v>7.4</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>13</v>
+      </c>
+      <c r="AQ13">
+        <v>22</v>
+      </c>
+      <c r="AR13">
+        <v>7.4</v>
+      </c>
+      <c r="AS13">
+        <v>7.8</v>
+      </c>
+      <c r="AT13">
+        <v>5.6</v>
+      </c>
+      <c r="AU13">
+        <v>12</v>
+      </c>
+      <c r="AV13">
+        <v>6.8</v>
+      </c>
+      <c r="AW13">
+        <v>7.6</v>
+      </c>
+      <c r="AX13">
+        <v>5.8</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>6.8</v>
+      </c>
+      <c r="BA13">
+        <v>7.6</v>
+      </c>
+      <c r="BB13">
+        <v>8.4</v>
+      </c>
+      <c r="BC13">
+        <v>16</v>
+      </c>
+      <c r="BD13">
+        <v>7</v>
+      </c>
+      <c r="BE13">
+        <v>7.6</v>
+      </c>
+      <c r="BF13">
+        <v>5.5</v>
+      </c>
+      <c r="BG13">
+        <v>7.8</v>
+      </c>
+      <c r="BH13">
+        <v>3.45</v>
+      </c>
+      <c r="BI13">
+        <v>2.86</v>
+      </c>
+      <c r="BJ13">
+        <v>15.5</v>
+      </c>
+      <c r="BK13">
+        <v>8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>15.5</v>
+      </c>
+      <c r="BN13">
+        <v>3.4</v>
+      </c>
+      <c r="BO13">
+        <v>2.82</v>
+      </c>
+      <c r="BP13">
+        <v>7.8</v>
+      </c>
+      <c r="BQ13">
+        <v>5.8</v>
+      </c>
+      <c r="BR13">
+        <v>34</v>
+      </c>
+      <c r="BS13">
+        <v>11</v>
+      </c>
+      <c r="BT13">
+        <v>17</v>
+      </c>
+      <c r="BU13">
+        <v>8.4</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>15</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>15</v>
+      </c>
+      <c r="BZ13">
+        <v>16.5</v>
+      </c>
+      <c r="CA13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14">
+        <v>2.24</v>
+      </c>
+      <c r="G14">
+        <v>2.44</v>
+      </c>
+      <c r="H14">
+        <v>3.4</v>
+      </c>
+      <c r="I14">
+        <v>3.9</v>
+      </c>
+      <c r="J14">
+        <v>3.25</v>
+      </c>
+      <c r="K14">
+        <v>3.7</v>
+      </c>
+      <c r="L14">
+        <v>1.43</v>
+      </c>
+      <c r="M14">
+        <v>1.08</v>
+      </c>
+      <c r="N14">
+        <v>3.05</v>
+      </c>
+      <c r="O14">
+        <v>1.36</v>
+      </c>
+      <c r="P14">
+        <v>1.74</v>
+      </c>
+      <c r="Q14">
+        <v>2.06</v>
+      </c>
+      <c r="R14">
+        <v>1.28</v>
+      </c>
+      <c r="S14">
+        <v>3.75</v>
+      </c>
+      <c r="T14">
+        <v>1.81</v>
+      </c>
+      <c r="U14">
+        <v>1.97</v>
+      </c>
+      <c r="V14">
+        <v>1.34</v>
+      </c>
+      <c r="W14">
+        <v>1.69</v>
+      </c>
+      <c r="X14">
+        <v>14</v>
+      </c>
+      <c r="Y14">
+        <v>13.5</v>
+      </c>
+      <c r="Z14">
+        <v>34</v>
+      </c>
+      <c r="AA14">
+        <v>95</v>
+      </c>
+      <c r="AB14">
+        <v>9.4</v>
+      </c>
+      <c r="AC14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14">
+        <v>16.5</v>
+      </c>
+      <c r="AE14">
+        <v>60</v>
+      </c>
+      <c r="AF14">
+        <v>15</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>80</v>
+      </c>
+      <c r="AJ14">
+        <v>42</v>
+      </c>
+      <c r="AK14">
+        <v>38</v>
+      </c>
+      <c r="AL14">
+        <v>50</v>
+      </c>
+      <c r="AM14">
+        <v>130</v>
+      </c>
+      <c r="AN14">
+        <v>23</v>
+      </c>
+      <c r="AO14">
+        <v>75</v>
+      </c>
+      <c r="AP14">
+        <v>9.4</v>
+      </c>
+      <c r="AQ14">
+        <v>9.6</v>
+      </c>
+      <c r="AR14">
+        <v>19.5</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>7</v>
+      </c>
+      <c r="AU14">
+        <v>6</v>
+      </c>
+      <c r="AV14">
+        <v>11.5</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>10.5</v>
+      </c>
+      <c r="AY14">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14">
+        <v>14</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
         <v>1.03</v>
       </c>
-      <c r="W12">
-        <v>1.3</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12">
-        <v>1.03</v>
-      </c>
-      <c r="AR12">
-        <v>1.03</v>
-      </c>
-      <c r="AS12">
-        <v>1.03</v>
-      </c>
-      <c r="AT12">
-        <v>1.03</v>
-      </c>
-      <c r="AU12">
-        <v>1.03</v>
-      </c>
-      <c r="AV12">
-        <v>1.03</v>
-      </c>
-      <c r="AW12">
-        <v>1.03</v>
-      </c>
-      <c r="AX12">
-        <v>1.03</v>
-      </c>
-      <c r="AY12">
-        <v>1.03</v>
-      </c>
-      <c r="AZ12">
-        <v>1.03</v>
-      </c>
-      <c r="BA12">
-        <v>1.03</v>
-      </c>
-      <c r="BB12">
-        <v>1.03</v>
-      </c>
-      <c r="BC12">
-        <v>1.03</v>
-      </c>
-      <c r="BD12">
-        <v>1.03</v>
-      </c>
-      <c r="BE12">
-        <v>1.03</v>
-      </c>
-      <c r="BF12">
-        <v>1.01</v>
-      </c>
-      <c r="BG12">
-        <v>1.01</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.01</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.01</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.01</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.01</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.01</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.01</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.01</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.01</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.01</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>112</v>
+      <c r="BC14">
+        <v>20</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>16.5</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>3.55</v>
+      </c>
+      <c r="BI14">
+        <v>2.64</v>
+      </c>
+      <c r="BJ14">
+        <v>11.5</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>5.7</v>
+      </c>
+      <c r="BO14">
+        <v>4</v>
+      </c>
+      <c r="BP14">
+        <v>20</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>38</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>7.8</v>
+      </c>
+      <c r="BU14">
+        <v>5.3</v>
+      </c>
+      <c r="BV14">
+        <v>36</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>55</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>36</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -376,7 +376,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 14:02:40</t>
+    <t>2026-08-11 16:11:59</t>
   </si>
 </sst>
 </file>
@@ -970,25 +970,25 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M2">
         <v>1.14</v>
@@ -1003,25 +1003,25 @@
         <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
         <v>7.8</v>
@@ -1039,7 +1039,7 @@
         <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -1048,10 +1048,10 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>26</v>
@@ -1066,7 +1066,7 @@
         <v>42</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1075,7 +1075,7 @@
         <v>42</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP2">
         <v>7.4</v>
@@ -1087,7 +1087,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1117,31 +1117,31 @@
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD2">
         <v>60</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH2">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1159,13 +1159,13 @@
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>6.4</v>
@@ -1230,13 +1230,13 @@
         <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
         <v>1.55</v>
@@ -1245,7 +1245,7 @@
         <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1257,7 +1257,7 @@
         <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
         <v>1.17</v>
@@ -1266,16 +1266,16 @@
         <v>2.3</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB3">
         <v>6</v>
@@ -1287,91 +1287,91 @@
         <v>32</v>
       </c>
       <c r="AE3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AM3">
         <v>300</v>
       </c>
       <c r="AN3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO3">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP3">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR3">
         <v>42</v>
       </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW3">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AX3">
         <v>7.6</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA3">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BB3">
         <v>16</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BF3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BH3">
         <v>2.86</v>
@@ -1389,7 +1389,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
@@ -1398,7 +1398,7 @@
         <v>3.45</v>
       </c>
       <c r="BP3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3">
         <v>8.800000000000001</v>
@@ -1407,19 +1407,19 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1431,7 +1431,7 @@
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -1454,19 +1454,19 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
         <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="I4">
         <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1475,25 +1475,25 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
+        <v>1.27</v>
+      </c>
+      <c r="O4">
+        <v>1.54</v>
+      </c>
+      <c r="P4">
         <v>1.26</v>
       </c>
-      <c r="O4">
-        <v>1.59</v>
-      </c>
-      <c r="P4">
-        <v>1.25</v>
-      </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
         <v>1.12</v>
       </c>
       <c r="S4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G5">
         <v>3.45</v>
@@ -1705,10 +1705,10 @@
         <v>2.68</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K5">
         <v>3.15</v>
@@ -1717,19 +1717,19 @@
         <v>1.53</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
         <v>2.46</v>
       </c>
       <c r="O5">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.16</v>
@@ -1738,13 +1738,13 @@
         <v>5.2</v>
       </c>
       <c r="T5">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
         <v>1.43</v>
@@ -1861,7 +1861,7 @@
         <v>2.68</v>
       </c>
       <c r="BI5">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5">
         <v>12</v>
@@ -1938,7 +1938,7 @@
         <v>111</v>
       </c>
       <c r="F6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G6">
         <v>2.04</v>
@@ -1947,43 +1947,43 @@
         <v>4.9</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L6">
         <v>1.56</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
         <v>2.56</v>
       </c>
       <c r="O6">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
         <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="V6">
         <v>1.18</v>
@@ -1995,7 +1995,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z6">
         <v>48</v>
@@ -2004,10 +2004,10 @@
         <v>200</v>
       </c>
       <c r="AB6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
         <v>27</v>
@@ -2016,7 +2016,7 @@
         <v>130</v>
       </c>
       <c r="AF6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
         <v>13</v>
@@ -2049,37 +2049,37 @@
         <v>6.6</v>
       </c>
       <c r="AQ6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT6">
         <v>4.9</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW6">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6">
         <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB6">
         <v>18</v>
@@ -2088,16 +2088,16 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG6">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2109,7 +2109,7 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2133,22 +2133,22 @@
         <v>46</v>
       </c>
       <c r="BS6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT6">
         <v>9.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV6">
         <v>70</v>
       </c>
       <c r="BW6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY6">
         <v>5.8</v>
@@ -2180,10 +2180,10 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -2207,19 +2207,19 @@
         <v>2.36</v>
       </c>
       <c r="O7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
         <v>1.17</v>
       </c>
       <c r="S7">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="T7">
         <v>2.16</v>
@@ -2228,10 +2228,10 @@
         <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -2291,13 +2291,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR7">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT7">
         <v>5.9</v>
@@ -2309,7 +2309,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2321,25 +2321,25 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
         <v>2.64</v>
@@ -2431,13 +2431,13 @@
         <v>1.56</v>
       </c>
       <c r="I8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J8">
         <v>3.7</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>1.45</v>
@@ -2446,13 +2446,13 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -2464,13 +2464,13 @@
         <v>4.1</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V8">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="W8">
         <v>1.12</v>
@@ -2494,7 +2494,7 @@
         <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE8">
         <v>24</v>
@@ -2545,40 +2545,40 @@
         <v>15</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
         <v>8</v>
       </c>
       <c r="AW8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG8">
         <v>9.6</v>
@@ -2679,7 +2679,7 @@
         <v>1.02</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2688,22 +2688,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R9">
         <v>1.12</v>
       </c>
       <c r="S9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2772,52 +2772,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2921,7 +2921,7 @@
         <v>1.02</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2930,22 +2930,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P10">
         <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
         <v>1.12</v>
       </c>
       <c r="S10">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3014,52 +3014,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3148,64 +3148,64 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G11">
         <v>2.86</v>
       </c>
       <c r="H11">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I11">
         <v>3.25</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11">
+        <v>3.65</v>
+      </c>
+      <c r="L11">
+        <v>1.43</v>
+      </c>
+      <c r="M11">
+        <v>1.08</v>
+      </c>
+      <c r="N11">
+        <v>3.25</v>
+      </c>
+      <c r="O11">
+        <v>1.38</v>
+      </c>
+      <c r="P11">
+        <v>1.75</v>
+      </c>
+      <c r="Q11">
+        <v>2.08</v>
+      </c>
+      <c r="R11">
+        <v>1.29</v>
+      </c>
+      <c r="S11">
         <v>3.8</v>
       </c>
-      <c r="L11">
-        <v>1.41</v>
-      </c>
-      <c r="M11">
-        <v>1.07</v>
-      </c>
-      <c r="N11">
-        <v>3.45</v>
-      </c>
-      <c r="O11">
-        <v>1.33</v>
-      </c>
-      <c r="P11">
-        <v>1.93</v>
-      </c>
-      <c r="Q11">
-        <v>1.97</v>
-      </c>
-      <c r="R11">
-        <v>1.32</v>
-      </c>
-      <c r="S11">
-        <v>3.5</v>
-      </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V11">
         <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X11">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11">
         <v>21</v>
@@ -3214,7 +3214,7 @@
         <v>55</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC11">
         <v>8.199999999999999</v>
@@ -3235,31 +3235,31 @@
         <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
         <v>42</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>120</v>
       </c>
       <c r="AN11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR11">
         <v>15</v>
@@ -3268,106 +3268,106 @@
         <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY11">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>3.25</v>
+      </c>
+      <c r="BI11">
+        <v>2.84</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>5.3</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>10</v>
-      </c>
-      <c r="AZ11">
-        <v>14.5</v>
-      </c>
-      <c r="BA11">
-        <v>1.01</v>
-      </c>
-      <c r="BB11">
-        <v>1.01</v>
-      </c>
-      <c r="BC11">
-        <v>23</v>
-      </c>
-      <c r="BD11">
-        <v>1.01</v>
-      </c>
-      <c r="BE11">
-        <v>1.01</v>
-      </c>
-      <c r="BF11">
-        <v>19.5</v>
-      </c>
-      <c r="BG11">
-        <v>1.01</v>
-      </c>
-      <c r="BH11">
-        <v>3.45</v>
-      </c>
-      <c r="BI11">
-        <v>2.76</v>
-      </c>
-      <c r="BJ11">
-        <v>10</v>
-      </c>
-      <c r="BK11">
-        <v>7.2</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP11">
         <v>22</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU11">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
         <v>25</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>120</v>
@@ -3390,16 +3390,16 @@
         <v>117</v>
       </c>
       <c r="F12">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
         <v>3.15</v>
@@ -3417,13 +3417,13 @@
         <v>2.46</v>
       </c>
       <c r="O12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P12">
         <v>1.49</v>
       </c>
       <c r="Q12">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
         <v>1.18</v>
@@ -3438,10 +3438,10 @@
         <v>1.66</v>
       </c>
       <c r="V12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X12">
         <v>8.199999999999999</v>
@@ -3468,7 +3468,7 @@
         <v>130</v>
       </c>
       <c r="AF12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
         <v>12</v>
@@ -3480,7 +3480,7 @@
         <v>160</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK12">
         <v>30</v>
@@ -3492,7 +3492,7 @@
         <v>320</v>
       </c>
       <c r="AN12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO12">
         <v>230</v>
@@ -3504,22 +3504,22 @@
         <v>10.5</v>
       </c>
       <c r="AR12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS12">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU12">
         <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW12">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX12">
         <v>9.4</v>
@@ -3528,88 +3528,88 @@
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BA12">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB12">
         <v>18.5</v>
       </c>
       <c r="BC12">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD12">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF12">
         <v>20</v>
       </c>
       <c r="BG12">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12">
         <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="BN12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO12">
         <v>3.95</v>
       </c>
       <c r="BP12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BT12">
         <v>8.4</v>
       </c>
       <c r="BU12">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>13.5</v>
+        <v>2.22</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB12" t="s">
         <v>120</v>
@@ -3632,7 +3632,7 @@
         <v>118</v>
       </c>
       <c r="F13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G13">
         <v>1.35</v>
@@ -3647,7 +3647,7 @@
         <v>5.5</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>1.41</v>
@@ -3659,7 +3659,7 @@
         <v>3.45</v>
       </c>
       <c r="O13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P13">
         <v>1.85</v>
@@ -3674,10 +3674,10 @@
         <v>3.7</v>
       </c>
       <c r="T13">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="V13">
         <v>1.07</v>
@@ -3686,7 +3686,7 @@
         <v>3.85</v>
       </c>
       <c r="X13">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y13">
         <v>34</v>
@@ -3698,7 +3698,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC13">
         <v>14</v>
@@ -3710,7 +3710,7 @@
         <v>450</v>
       </c>
       <c r="AF13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -3746,10 +3746,10 @@
         <v>22</v>
       </c>
       <c r="AR13">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
         <v>5.6</v>
@@ -3758,10 +3758,10 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW13">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX13">
         <v>5.8</v>
@@ -3770,10 +3770,10 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA13">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB13">
         <v>8.4</v>
@@ -3782,19 +3782,19 @@
         <v>16</v>
       </c>
       <c r="BD13">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE13">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG13">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI13">
         <v>2.86</v>
@@ -3803,19 +3803,19 @@
         <v>15.5</v>
       </c>
       <c r="BK13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN13">
         <v>3.4</v>
       </c>
       <c r="BO13">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BP13">
         <v>7.8</v>
@@ -3827,31 +3827,31 @@
         <v>34</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT13">
         <v>17</v>
       </c>
       <c r="BU13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BZ13">
         <v>16.5</v>
       </c>
       <c r="CA13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="s">
         <v>120</v>
@@ -3874,22 +3874,22 @@
         <v>119</v>
       </c>
       <c r="F14">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G14">
         <v>2.44</v>
       </c>
       <c r="H14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L14">
         <v>1.43</v>
@@ -3898,13 +3898,13 @@
         <v>1.08</v>
       </c>
       <c r="N14">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O14">
         <v>1.36</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
         <v>2.06</v>
@@ -3916,13 +3916,13 @@
         <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
         <v>1.69</v>
@@ -3931,13 +3931,13 @@
         <v>14</v>
       </c>
       <c r="Y14">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
         <v>34</v>
       </c>
       <c r="AA14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB14">
         <v>9.4</v>
@@ -3946,10 +3946,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF14">
         <v>15</v>
@@ -3961,7 +3961,7 @@
         <v>20</v>
       </c>
       <c r="AI14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ14">
         <v>42</v>
@@ -3979,7 +3979,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP14">
         <v>9.4</v>
@@ -3991,19 +3991,19 @@
         <v>19.5</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT14">
         <v>7</v>
       </c>
       <c r="AU14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
         <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX14">
         <v>10.5</v>
@@ -4015,25 +4015,25 @@
         <v>14</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC14">
         <v>20</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF14">
         <v>16.5</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH14">
         <v>3.55</v>
@@ -4045,13 +4045,13 @@
         <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN14">
         <v>5.7</v>
@@ -4063,13 +4063,13 @@
         <v>20</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR14">
         <v>38</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT14">
         <v>7.8</v>
@@ -4081,19 +4081,19 @@
         <v>36</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX14">
         <v>55</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BZ14">
         <v>36</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="s">
         <v>120</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
   <si>
     <t>League</t>
   </si>
@@ -322,6 +322,9 @@
     <t>CA Germinal</t>
   </si>
   <si>
+    <t>Club Cipolletti</t>
+  </si>
+  <si>
     <t>Independiente Chivilcoy</t>
   </si>
   <si>
@@ -361,6 +364,9 @@
     <t>Santamarina</t>
   </si>
   <si>
+    <t>Argentino Monte Maiz</t>
+  </si>
+  <si>
     <t>Sarmiento de Resistencia</t>
   </si>
   <si>
@@ -376,7 +382,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 16:11:59</t>
+    <t>2026-08-11 18:20:18</t>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -967,58 +973,58 @@
         <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.66</v>
@@ -1030,55 +1036,55 @@
         <v>9.6</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN2">
         <v>42</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
         <v>9</v>
@@ -1087,28 +1093,28 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
         <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>80</v>
@@ -1129,19 +1135,19 @@
         <v>36</v>
       </c>
       <c r="BG2">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BH2">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1150,10 +1156,10 @@
         <v>15</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
         <v>24</v>
@@ -1168,10 +1174,10 @@
         <v>12</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>38</v>
@@ -1183,7 +1189,7 @@
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>60</v>
@@ -1192,7 +1198,7 @@
         <v>12.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1209,13 +1215,13 @@
         <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H3">
         <v>6.2</v>
@@ -1227,7 +1233,7 @@
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.58</v>
@@ -1239,13 +1245,13 @@
         <v>2.74</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1254,19 +1260,19 @@
         <v>5.6</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
         <v>1.62</v>
       </c>
       <c r="V3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
         <v>16</v>
@@ -1275,22 +1281,22 @@
         <v>55</v>
       </c>
       <c r="AA3">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC3">
         <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE3">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1299,7 +1305,7 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AJ3">
         <v>18.5</v>
@@ -1311,13 +1317,13 @@
         <v>70</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO3">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AP3">
         <v>8.199999999999999</v>
@@ -1329,52 +1335,52 @@
         <v>42</v>
       </c>
       <c r="AS3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>25</v>
       </c>
       <c r="AW3">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA3">
-        <v>12.5</v>
+        <v>85</v>
       </c>
       <c r="BB3">
         <v>16</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH3">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI3">
         <v>2.5</v>
@@ -1389,13 +1395,13 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP3">
         <v>13.5</v>
@@ -1407,13 +1413,13 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1425,16 +1431,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1451,19 +1457,19 @@
         <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>1.5</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>2.2</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4">
         <v>1.06</v>
@@ -1475,25 +1481,25 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="P4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="R4">
         <v>1.12</v>
       </c>
       <c r="S4">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1562,58 +1568,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1676,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1693,25 +1699,25 @@
         <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F5">
         <v>3.05</v>
       </c>
       <c r="G5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H5">
         <v>2.68</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J5">
         <v>2.84</v>
       </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.53</v>
@@ -1726,7 +1732,7 @@
         <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
         <v>2.72</v>
@@ -1735,16 +1741,16 @@
         <v>1.16</v>
       </c>
       <c r="S5">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
         <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
         <v>1.43</v>
@@ -1765,7 +1771,7 @@
         <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
         <v>16</v>
@@ -1813,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT5">
         <v>6.8</v>
@@ -1825,37 +1831,37 @@
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX5">
         <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE5">
+        <v>5.3</v>
+      </c>
+      <c r="BF5">
+        <v>5.1</v>
+      </c>
+      <c r="BG5">
         <v>5</v>
-      </c>
-      <c r="BF5">
-        <v>4.8</v>
-      </c>
-      <c r="BG5">
-        <v>4.8</v>
       </c>
       <c r="BH5">
         <v>2.68</v>
@@ -1918,7 +1924,7 @@
         <v>9.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1935,7 +1941,7 @@
         <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6">
         <v>1.87</v>
@@ -1947,10 +1953,10 @@
         <v>4.9</v>
       </c>
       <c r="I6">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
         <v>3.5</v>
@@ -1959,13 +1965,13 @@
         <v>1.56</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
         <v>2.56</v>
       </c>
       <c r="O6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P6">
         <v>1.5</v>
@@ -1977,7 +1983,7 @@
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T6">
         <v>2.22</v>
@@ -1986,16 +1992,16 @@
         <v>1.67</v>
       </c>
       <c r="V6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X6">
         <v>9.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>48</v>
@@ -2004,10 +2010,10 @@
         <v>200</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
         <v>27</v>
@@ -2016,7 +2022,7 @@
         <v>130</v>
       </c>
       <c r="AF6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6">
         <v>13</v>
@@ -2049,34 +2055,34 @@
         <v>6.6</v>
       </c>
       <c r="AQ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="AS6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT6">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA6">
         <v>5.8</v>
@@ -2094,10 +2100,10 @@
         <v>5.9</v>
       </c>
       <c r="BF6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2127,10 +2133,10 @@
         <v>18</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS6">
         <v>5.4</v>
@@ -2151,16 +2157,16 @@
         <v>95</v>
       </c>
       <c r="BY6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BZ6">
         <v>50</v>
       </c>
       <c r="CA6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2177,7 +2183,7 @@
         <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F7">
         <v>2.68</v>
@@ -2186,16 +2192,16 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
         <v>2.76</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
         <v>1.6</v>
@@ -2210,7 +2216,7 @@
         <v>1.6</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q7">
         <v>2.78</v>
@@ -2225,10 +2231,10 @@
         <v>2.16</v>
       </c>
       <c r="U7">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.5</v>
@@ -2402,7 +2408,7 @@
         <v>9.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2419,13 +2425,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F8">
         <v>7.2</v>
       </c>
       <c r="G8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>1.56</v>
@@ -2455,7 +2461,7 @@
         <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R8">
         <v>1.25</v>
@@ -2464,7 +2470,7 @@
         <v>4.1</v>
       </c>
       <c r="T8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
         <v>1.67</v>
@@ -2539,16 +2545,16 @@
         <v>7</v>
       </c>
       <c r="AS8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU8">
         <v>7.8</v>
       </c>
       <c r="AV8">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
         <v>17</v>
@@ -2644,7 +2650,7 @@
         <v>5.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2661,19 +2667,19 @@
         <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F9">
         <v>1.02</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>1.02</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>1.02</v>
@@ -2688,22 +2694,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O9">
         <v>1.56</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q9">
         <v>1.56</v>
       </c>
       <c r="R9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2772,52 +2778,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2886,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2903,7 +2909,7 @@
         <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>1.02</v>
@@ -2930,22 +2936,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
+        <v>1.26</v>
+      </c>
+      <c r="O10">
+        <v>1.56</v>
+      </c>
+      <c r="P10">
         <v>1.25</v>
       </c>
-      <c r="O10">
-        <v>1.43</v>
-      </c>
-      <c r="P10">
-        <v>1.24</v>
-      </c>
       <c r="Q10">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="R10">
         <v>1.12</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3014,52 +3020,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3122,171 +3128,171 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>2.52</v>
+        <v>1.02</v>
       </c>
       <c r="G11">
-        <v>2.86</v>
+        <v>110</v>
       </c>
       <c r="H11">
-        <v>2.84</v>
+        <v>1.02</v>
       </c>
       <c r="I11">
-        <v>3.25</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="S11">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
         <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
         <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
         <v>1.01</v>
@@ -3295,7 +3301,7 @@
         <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
         <v>1.01</v>
@@ -3310,309 +3316,309 @@
         <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
         <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>2.56</v>
       </c>
       <c r="G12">
-        <v>2.04</v>
+        <v>2.86</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L12">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="M12">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="P12">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="U12">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="X12">
+        <v>14</v>
+      </c>
+      <c r="Y12">
+        <v>11.5</v>
+      </c>
+      <c r="Z12">
+        <v>21</v>
+      </c>
+      <c r="AA12">
+        <v>55</v>
+      </c>
+      <c r="AB12">
+        <v>10.5</v>
+      </c>
+      <c r="AC12">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y12">
-        <v>12</v>
-      </c>
-      <c r="Z12">
-        <v>46</v>
-      </c>
-      <c r="AA12">
-        <v>190</v>
-      </c>
-      <c r="AB12">
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12">
+        <v>38</v>
+      </c>
+      <c r="AF12">
+        <v>18.5</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>55</v>
+      </c>
+      <c r="AJ12">
+        <v>42</v>
+      </c>
+      <c r="AK12">
+        <v>34</v>
+      </c>
+      <c r="AL12">
+        <v>50</v>
+      </c>
+      <c r="AM12">
+        <v>120</v>
+      </c>
+      <c r="AN12">
+        <v>32</v>
+      </c>
+      <c r="AO12">
+        <v>40</v>
+      </c>
+      <c r="AP12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12">
+        <v>8.4</v>
+      </c>
+      <c r="AR12">
+        <v>17</v>
+      </c>
+      <c r="AS12">
+        <v>7.2</v>
+      </c>
+      <c r="AT12">
+        <v>8.4</v>
+      </c>
+      <c r="AU12">
+        <v>6.6</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>6.8</v>
+      </c>
+      <c r="AX12">
+        <v>14.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12">
+        <v>7.2</v>
+      </c>
+      <c r="BB12">
+        <v>6.8</v>
+      </c>
+      <c r="BC12">
+        <v>6.6</v>
+      </c>
+      <c r="BD12">
+        <v>7</v>
+      </c>
+      <c r="BE12">
+        <v>7.8</v>
+      </c>
+      <c r="BF12">
+        <v>6.6</v>
+      </c>
+      <c r="BG12">
+        <v>6.8</v>
+      </c>
+      <c r="BH12">
+        <v>3.25</v>
+      </c>
+      <c r="BI12">
+        <v>2.84</v>
+      </c>
+      <c r="BJ12">
+        <v>10.5</v>
+      </c>
+      <c r="BK12">
+        <v>5.3</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>10</v>
+      </c>
+      <c r="BN12">
+        <v>5.8</v>
+      </c>
+      <c r="BO12">
+        <v>4.8</v>
+      </c>
+      <c r="BP12">
+        <v>22</v>
+      </c>
+      <c r="BQ12">
+        <v>7.2</v>
+      </c>
+      <c r="BR12">
+        <v>38</v>
+      </c>
+      <c r="BS12">
+        <v>8.4</v>
+      </c>
+      <c r="BT12">
         <v>6.2</v>
       </c>
-      <c r="AC12">
-        <v>7.8</v>
-      </c>
-      <c r="AD12">
-        <v>950</v>
-      </c>
-      <c r="AE12">
-        <v>130</v>
-      </c>
-      <c r="AF12">
-        <v>12.5</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>36</v>
-      </c>
-      <c r="AI12">
-        <v>160</v>
-      </c>
-      <c r="AJ12">
-        <v>30</v>
-      </c>
-      <c r="AK12">
-        <v>30</v>
-      </c>
-      <c r="AL12">
-        <v>85</v>
-      </c>
-      <c r="AM12">
-        <v>320</v>
-      </c>
-      <c r="AN12">
+      <c r="BU12">
+        <v>5.1</v>
+      </c>
+      <c r="BV12">
+        <v>25</v>
+      </c>
+      <c r="BW12">
+        <v>7.6</v>
+      </c>
+      <c r="BX12">
+        <v>40</v>
+      </c>
+      <c r="BY12">
+        <v>8.6</v>
+      </c>
+      <c r="BZ12">
         <v>34</v>
       </c>
-      <c r="AO12">
-        <v>230</v>
-      </c>
-      <c r="AP12">
-        <v>7.2</v>
-      </c>
-      <c r="AQ12">
-        <v>10.5</v>
-      </c>
-      <c r="AR12">
-        <v>8</v>
-      </c>
-      <c r="AS12">
-        <v>9.4</v>
-      </c>
-      <c r="AT12">
-        <v>5.5</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>7</v>
-      </c>
-      <c r="AW12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX12">
-        <v>9.4</v>
-      </c>
-      <c r="AY12">
-        <v>10</v>
-      </c>
-      <c r="AZ12">
-        <v>22</v>
-      </c>
-      <c r="BA12">
-        <v>9.4</v>
-      </c>
-      <c r="BB12">
-        <v>18.5</v>
-      </c>
-      <c r="BC12">
-        <v>7.4</v>
-      </c>
-      <c r="BD12">
-        <v>9</v>
-      </c>
-      <c r="BE12">
-        <v>9.6</v>
-      </c>
-      <c r="BF12">
-        <v>20</v>
-      </c>
-      <c r="BG12">
-        <v>9.6</v>
-      </c>
-      <c r="BH12">
-        <v>2.6</v>
-      </c>
-      <c r="BI12">
-        <v>2.3</v>
-      </c>
-      <c r="BJ12">
-        <v>12.5</v>
-      </c>
-      <c r="BK12">
-        <v>7.8</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.3</v>
-      </c>
-      <c r="BN12">
-        <v>4.3</v>
-      </c>
-      <c r="BO12">
-        <v>3.95</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>14</v>
-      </c>
-      <c r="BT12">
-        <v>8.4</v>
-      </c>
-      <c r="BU12">
-        <v>6</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>2.22</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>16.5</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
       <c r="CA12">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3629,237 +3635,237 @@
         <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F13">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="G13">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="H13">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="J13">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="K13">
+        <v>3.35</v>
+      </c>
+      <c r="L13">
+        <v>1.62</v>
+      </c>
+      <c r="M13">
+        <v>1.14</v>
+      </c>
+      <c r="N13">
+        <v>2.46</v>
+      </c>
+      <c r="O13">
+        <v>1.61</v>
+      </c>
+      <c r="P13">
+        <v>1.49</v>
+      </c>
+      <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>1.18</v>
+      </c>
+      <c r="S13">
         <v>6</v>
       </c>
-      <c r="L13">
-        <v>1.41</v>
-      </c>
-      <c r="M13">
-        <v>1.07</v>
-      </c>
-      <c r="N13">
-        <v>3.45</v>
-      </c>
-      <c r="O13">
-        <v>1.36</v>
-      </c>
-      <c r="P13">
-        <v>1.85</v>
-      </c>
-      <c r="Q13">
-        <v>2.02</v>
-      </c>
-      <c r="R13">
-        <v>1.31</v>
-      </c>
-      <c r="S13">
-        <v>3.7</v>
-      </c>
       <c r="T13">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="V13">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>3.85</v>
+        <v>1.96</v>
       </c>
       <c r="X13">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB13">
         <v>6.2</v>
       </c>
       <c r="AC13">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AE13">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AF13">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AI13">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="AJ13">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AK13">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AL13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM13">
-        <v>520</v>
+        <v>320</v>
       </c>
       <c r="AN13">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP13">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AR13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS13">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU13">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW13">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX13">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AY13">
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BA13">
+        <v>9</v>
+      </c>
+      <c r="BB13">
+        <v>18.5</v>
+      </c>
+      <c r="BC13">
+        <v>7.2</v>
+      </c>
+      <c r="BD13">
+        <v>8.6</v>
+      </c>
+      <c r="BE13">
+        <v>9.4</v>
+      </c>
+      <c r="BF13">
+        <v>20</v>
+      </c>
+      <c r="BG13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH13">
+        <v>2.6</v>
+      </c>
+      <c r="BI13">
+        <v>2.3</v>
+      </c>
+      <c r="BJ13">
+        <v>12.5</v>
+      </c>
+      <c r="BK13">
+        <v>7.8</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>2.3</v>
+      </c>
+      <c r="BN13">
+        <v>4.3</v>
+      </c>
+      <c r="BO13">
+        <v>3.95</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>14</v>
+      </c>
+      <c r="BT13">
         <v>8.4</v>
       </c>
-      <c r="BB13">
-        <v>8.4</v>
-      </c>
-      <c r="BC13">
-        <v>16</v>
-      </c>
-      <c r="BD13">
-        <v>7.6</v>
-      </c>
-      <c r="BE13">
-        <v>8.4</v>
-      </c>
-      <c r="BF13">
-        <v>5.6</v>
-      </c>
-      <c r="BG13">
-        <v>8.6</v>
-      </c>
-      <c r="BH13">
-        <v>3.4</v>
-      </c>
-      <c r="BI13">
-        <v>2.86</v>
-      </c>
-      <c r="BJ13">
-        <v>15.5</v>
-      </c>
-      <c r="BK13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>17</v>
-      </c>
-      <c r="BN13">
-        <v>3.4</v>
-      </c>
-      <c r="BO13">
-        <v>2.86</v>
-      </c>
-      <c r="BP13">
-        <v>7.8</v>
-      </c>
-      <c r="BQ13">
-        <v>5.8</v>
-      </c>
-      <c r="BR13">
-        <v>34</v>
-      </c>
-      <c r="BS13">
-        <v>11.5</v>
-      </c>
-      <c r="BT13">
-        <v>17</v>
-      </c>
       <c r="BU13">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>16</v>
+        <v>2.22</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BZ13">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
@@ -3871,232 +3877,474 @@
         <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F14">
-        <v>2.18</v>
+        <v>1.31</v>
       </c>
       <c r="G14">
-        <v>2.44</v>
+        <v>1.35</v>
       </c>
       <c r="H14">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="I14">
+        <v>15.5</v>
+      </c>
+      <c r="J14">
+        <v>5.5</v>
+      </c>
+      <c r="K14">
+        <v>6</v>
+      </c>
+      <c r="L14">
+        <v>1.41</v>
+      </c>
+      <c r="M14">
+        <v>1.07</v>
+      </c>
+      <c r="N14">
+        <v>3.5</v>
+      </c>
+      <c r="O14">
+        <v>1.35</v>
+      </c>
+      <c r="P14">
+        <v>1.86</v>
+      </c>
+      <c r="Q14">
+        <v>2.02</v>
+      </c>
+      <c r="R14">
+        <v>1.33</v>
+      </c>
+      <c r="S14">
+        <v>3.7</v>
+      </c>
+      <c r="T14">
+        <v>2.66</v>
+      </c>
+      <c r="U14">
+        <v>1.56</v>
+      </c>
+      <c r="V14">
+        <v>1.06</v>
+      </c>
+      <c r="W14">
         <v>3.85</v>
       </c>
-      <c r="J14">
-        <v>3.2</v>
-      </c>
-      <c r="K14">
-        <v>3.75</v>
-      </c>
-      <c r="L14">
-        <v>1.43</v>
-      </c>
-      <c r="M14">
-        <v>1.08</v>
-      </c>
-      <c r="N14">
-        <v>3.15</v>
-      </c>
-      <c r="O14">
-        <v>1.36</v>
-      </c>
-      <c r="P14">
-        <v>1.75</v>
-      </c>
-      <c r="Q14">
-        <v>2.06</v>
-      </c>
-      <c r="R14">
-        <v>1.28</v>
-      </c>
-      <c r="S14">
-        <v>3.75</v>
-      </c>
-      <c r="T14">
-        <v>1.82</v>
-      </c>
-      <c r="U14">
-        <v>1.96</v>
-      </c>
-      <c r="V14">
-        <v>1.35</v>
-      </c>
-      <c r="W14">
-        <v>1.69</v>
-      </c>
       <c r="X14">
+        <v>17.5</v>
+      </c>
+      <c r="Y14">
+        <v>34</v>
+      </c>
+      <c r="Z14">
+        <v>170</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>6.4</v>
+      </c>
+      <c r="AC14">
         <v>14</v>
       </c>
-      <c r="Y14">
-        <v>12.5</v>
-      </c>
-      <c r="Z14">
-        <v>34</v>
-      </c>
-      <c r="AA14">
-        <v>85</v>
-      </c>
-      <c r="AB14">
-        <v>9.4</v>
-      </c>
-      <c r="AC14">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD14">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>430</v>
       </c>
       <c r="AF14">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AG14">
         <v>12</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AJ14">
-        <v>42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK14">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AM14">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AQ14">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="AR14">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS14">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AV14">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW14">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AX14">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY14">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="BA14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB14">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BC14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BD14">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BE14">
         <v>8</v>
       </c>
       <c r="BF14">
+        <v>5.6</v>
+      </c>
+      <c r="BG14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH14">
+        <v>3.4</v>
+      </c>
+      <c r="BI14">
+        <v>2.86</v>
+      </c>
+      <c r="BJ14">
+        <v>15.5</v>
+      </c>
+      <c r="BK14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>17</v>
+      </c>
+      <c r="BN14">
+        <v>3.4</v>
+      </c>
+      <c r="BO14">
+        <v>3.05</v>
+      </c>
+      <c r="BP14">
+        <v>7.8</v>
+      </c>
+      <c r="BQ14">
+        <v>5.8</v>
+      </c>
+      <c r="BR14">
+        <v>34</v>
+      </c>
+      <c r="BS14">
+        <v>11.5</v>
+      </c>
+      <c r="BT14">
+        <v>17</v>
+      </c>
+      <c r="BU14">
+        <v>8.6</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>16</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>16</v>
+      </c>
+      <c r="BZ14">
         <v>16.5</v>
       </c>
-      <c r="BG14">
+      <c r="CA14">
+        <v>8.6</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15">
+        <v>2.18</v>
+      </c>
+      <c r="G15">
+        <v>2.46</v>
+      </c>
+      <c r="H15">
+        <v>3.25</v>
+      </c>
+      <c r="I15">
+        <v>3.85</v>
+      </c>
+      <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
+        <v>3.75</v>
+      </c>
+      <c r="L15">
+        <v>1.43</v>
+      </c>
+      <c r="M15">
+        <v>1.08</v>
+      </c>
+      <c r="N15">
+        <v>3.05</v>
+      </c>
+      <c r="O15">
+        <v>1.36</v>
+      </c>
+      <c r="P15">
+        <v>1.75</v>
+      </c>
+      <c r="Q15">
+        <v>2.06</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>3.75</v>
+      </c>
+      <c r="T15">
+        <v>1.82</v>
+      </c>
+      <c r="U15">
+        <v>1.96</v>
+      </c>
+      <c r="V15">
+        <v>1.35</v>
+      </c>
+      <c r="W15">
+        <v>1.69</v>
+      </c>
+      <c r="X15">
+        <v>14</v>
+      </c>
+      <c r="Y15">
+        <v>12.5</v>
+      </c>
+      <c r="Z15">
+        <v>34</v>
+      </c>
+      <c r="AA15">
+        <v>80</v>
+      </c>
+      <c r="AB15">
+        <v>9.4</v>
+      </c>
+      <c r="AC15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>15.5</v>
+      </c>
+      <c r="AE15">
+        <v>55</v>
+      </c>
+      <c r="AF15">
+        <v>15</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <v>65</v>
+      </c>
+      <c r="AJ15">
         <v>42</v>
       </c>
-      <c r="BH14">
+      <c r="AK15">
+        <v>38</v>
+      </c>
+      <c r="AL15">
+        <v>46</v>
+      </c>
+      <c r="AM15">
+        <v>130</v>
+      </c>
+      <c r="AN15">
+        <v>23</v>
+      </c>
+      <c r="AO15">
+        <v>60</v>
+      </c>
+      <c r="AP15">
+        <v>9.6</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>18.5</v>
+      </c>
+      <c r="AS15">
+        <v>7.8</v>
+      </c>
+      <c r="AT15">
+        <v>7</v>
+      </c>
+      <c r="AU15">
+        <v>6.6</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>7.4</v>
+      </c>
+      <c r="AX15">
+        <v>11</v>
+      </c>
+      <c r="AY15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>14.5</v>
+      </c>
+      <c r="BA15">
+        <v>7.6</v>
+      </c>
+      <c r="BB15">
+        <v>6.8</v>
+      </c>
+      <c r="BC15">
+        <v>20</v>
+      </c>
+      <c r="BD15">
+        <v>32</v>
+      </c>
+      <c r="BE15">
+        <v>8</v>
+      </c>
+      <c r="BF15">
+        <v>16.5</v>
+      </c>
+      <c r="BG15">
+        <v>7.6</v>
+      </c>
+      <c r="BH15">
         <v>3.55</v>
       </c>
-      <c r="BI14">
+      <c r="BI15">
         <v>2.64</v>
       </c>
-      <c r="BJ14">
+      <c r="BJ15">
         <v>11.5</v>
       </c>
-      <c r="BK14">
+      <c r="BK15">
         <v>3.85</v>
       </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
         <v>5.6</v>
       </c>
-      <c r="BN14">
+      <c r="BN15">
         <v>5.7</v>
       </c>
-      <c r="BO14">
+      <c r="BO15">
         <v>4</v>
       </c>
-      <c r="BP14">
+      <c r="BP15">
         <v>20</v>
       </c>
-      <c r="BQ14">
+      <c r="BQ15">
         <v>4.5</v>
       </c>
-      <c r="BR14">
+      <c r="BR15">
         <v>38</v>
       </c>
-      <c r="BS14">
+      <c r="BS15">
         <v>5</v>
       </c>
-      <c r="BT14">
+      <c r="BT15">
         <v>7.8</v>
       </c>
-      <c r="BU14">
+      <c r="BU15">
         <v>5.3</v>
       </c>
-      <c r="BV14">
+      <c r="BV15">
         <v>36</v>
       </c>
-      <c r="BW14">
+      <c r="BW15">
         <v>5</v>
       </c>
-      <c r="BX14">
+      <c r="BX15">
         <v>55</v>
       </c>
-      <c r="BY14">
+      <c r="BY15">
         <v>5.2</v>
       </c>
-      <c r="BZ14">
+      <c r="BZ15">
         <v>36</v>
       </c>
-      <c r="CA14">
+      <c r="CA15">
         <v>5</v>
       </c>
-      <c r="CB14" t="s">
-        <v>120</v>
+      <c r="CB15" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -382,7 +382,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 18:20:18</t>
+    <t>2026-08-11 20:28:29</t>
   </si>
 </sst>
 </file>
@@ -985,58 +985,58 @@
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
+        <v>2.98</v>
+      </c>
+      <c r="K2">
+        <v>3.05</v>
+      </c>
+      <c r="L2">
+        <v>1.69</v>
+      </c>
+      <c r="M2">
+        <v>1.15</v>
+      </c>
+      <c r="N2">
+        <v>2.48</v>
+      </c>
+      <c r="O2">
+        <v>1.64</v>
+      </c>
+      <c r="P2">
+        <v>1.47</v>
+      </c>
+      <c r="Q2">
         <v>3</v>
       </c>
-      <c r="K2">
-        <v>3.1</v>
-      </c>
-      <c r="L2">
-        <v>1.65</v>
-      </c>
-      <c r="M2">
-        <v>1.14</v>
-      </c>
-      <c r="N2">
-        <v>2.54</v>
-      </c>
-      <c r="O2">
-        <v>1.63</v>
-      </c>
-      <c r="P2">
-        <v>1.51</v>
-      </c>
-      <c r="Q2">
-        <v>2.92</v>
-      </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
         <v>1.66</v>
       </c>
       <c r="X2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
         <v>9.6</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA2">
         <v>80</v>
@@ -1048,46 +1048,46 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
         <v>20</v>
@@ -1108,7 +1108,7 @@
         <v>55</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
         <v>11.5</v>
@@ -1123,37 +1123,37 @@
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="BF2">
         <v>36</v>
       </c>
       <c r="BG2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH2">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="BN2">
         <v>5</v>
@@ -1165,37 +1165,37 @@
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BR2">
         <v>50</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="s">
         <v>122</v>
@@ -1218,7 +1218,7 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G3">
         <v>1.77</v>
@@ -1227,13 +1227,13 @@
         <v>6.2</v>
       </c>
       <c r="I3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.58</v>
@@ -1254,16 +1254,16 @@
         <v>2.7</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
         <v>1.18</v>
@@ -1272,37 +1272,37 @@
         <v>2.28</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA3">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE3">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3">
         <v>200</v>
@@ -1311,7 +1311,7 @@
         <v>18.5</v>
       </c>
       <c r="AK3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL3">
         <v>70</v>
@@ -1320,67 +1320,67 @@
         <v>280</v>
       </c>
       <c r="AN3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO3">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
         <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW3">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
         <v>22</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BF3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI3">
         <v>2.5</v>
@@ -1395,7 +1395,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
@@ -1413,31 +1413,31 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>122</v>
@@ -1472,7 +1472,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1484,22 +1484,22 @@
         <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O4">
         <v>1.3</v>
       </c>
       <c r="P4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q4">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
         <v>1.12</v>
       </c>
       <c r="S4">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1526,7 +1526,7 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC4">
         <v>1000</v>
@@ -1538,10 +1538,10 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH4">
         <v>1000</v>
@@ -1550,19 +1550,19 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1616,10 +1616,10 @@
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1708,7 +1708,7 @@
         <v>3.4</v>
       </c>
       <c r="H5">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I5">
         <v>2.94</v>
@@ -1720,7 +1720,7 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
         <v>1.12</v>
@@ -1729,7 +1729,7 @@
         <v>2.46</v>
       </c>
       <c r="O5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P5">
         <v>1.49</v>
@@ -1756,16 +1756,16 @@
         <v>1.43</v>
       </c>
       <c r="X5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5">
         <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>10.5</v>
@@ -1777,34 +1777,34 @@
         <v>16</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>24</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AJ5">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AK5">
         <v>65</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>460</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN5">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AO5">
         <v>65</v>
@@ -1819,19 +1819,19 @@
         <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT5">
         <v>6.8</v>
       </c>
       <c r="AU5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV5">
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX5">
         <v>15.5</v>
@@ -1843,25 +1843,25 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB5">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC5">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BD5">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE5">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF5">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BH5">
         <v>2.68</v>
@@ -1947,10 +1947,10 @@
         <v>1.87</v>
       </c>
       <c r="G6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5.9</v>
@@ -1959,7 +1959,7 @@
         <v>3.05</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
         <v>1.56</v>
@@ -1986,7 +1986,7 @@
         <v>5.3</v>
       </c>
       <c r="T6">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
         <v>1.67</v>
@@ -2007,7 +2007,7 @@
         <v>48</v>
       </c>
       <c r="AA6">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB6">
         <v>6.6</v>
@@ -2025,13 +2025,13 @@
         <v>11</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6">
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ6">
         <v>28</v>
@@ -2043,13 +2043,13 @@
         <v>75</v>
       </c>
       <c r="AM6">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN6">
         <v>28</v>
       </c>
       <c r="AO6">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP6">
         <v>6.6</v>
@@ -2058,10 +2058,10 @@
         <v>10</v>
       </c>
       <c r="AR6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT6">
         <v>5.4</v>
@@ -2073,7 +2073,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX6">
         <v>8.800000000000001</v>
@@ -2085,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="BA6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB6">
         <v>18</v>
@@ -2094,16 +2094,16 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF6">
         <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2186,19 +2186,19 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>3.45</v>
       </c>
       <c r="J7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K7">
         <v>3.15</v>
@@ -2231,10 +2231,10 @@
         <v>2.16</v>
       </c>
       <c r="U7">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
         <v>1.5</v>
@@ -2282,10 +2282,10 @@
         <v>48</v>
       </c>
       <c r="AL7">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AM7">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN7">
         <v>80</v>
@@ -2294,7 +2294,7 @@
         <v>100</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7">
         <v>7.2</v>
@@ -2306,10 +2306,10 @@
         <v>8</v>
       </c>
       <c r="AT7">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV7">
         <v>11</v>
@@ -2342,7 +2342,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
         <v>8.199999999999999</v>
@@ -2440,7 +2440,7 @@
         <v>1.65</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>4.2</v>
@@ -2473,10 +2473,10 @@
         <v>2.24</v>
       </c>
       <c r="U8">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="W8">
         <v>1.12</v>
@@ -2485,7 +2485,7 @@
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z8">
         <v>8.6</v>
@@ -2497,7 +2497,7 @@
         <v>23</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>11</v>
@@ -2506,7 +2506,7 @@
         <v>24</v>
       </c>
       <c r="AF8">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AG8">
         <v>36</v>
@@ -2515,7 +2515,7 @@
         <v>34</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
         <v>360</v>
@@ -2527,13 +2527,13 @@
         <v>180</v>
       </c>
       <c r="AM8">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AN8">
         <v>340</v>
       </c>
       <c r="AO8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AP8">
         <v>8.800000000000001</v>
@@ -2560,31 +2560,31 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY8">
         <v>26</v>
       </c>
       <c r="AZ8">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA8">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB8">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC8">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE8">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF8">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
         <v>9.6</v>
@@ -2670,22 +2670,22 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2694,7 +2694,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O9">
         <v>1.56</v>
@@ -2718,10 +2718,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2736,10 +2736,10 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2748,10 +2748,10 @@
         <v>1000</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH9">
         <v>1000</v>
@@ -2760,76 +2760,76 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2951,7 +2951,7 @@
         <v>1.12</v>
       </c>
       <c r="S10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3402,19 +3402,19 @@
         <v>2.86</v>
       </c>
       <c r="H12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J12">
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
         <v>1.08</v>
@@ -3438,10 +3438,10 @@
         <v>3.85</v>
       </c>
       <c r="T12">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -3465,7 +3465,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>14</v>
@@ -3501,7 +3501,7 @@
         <v>32</v>
       </c>
       <c r="AO12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP12">
         <v>9.199999999999999</v>
@@ -3513,7 +3513,7 @@
         <v>17</v>
       </c>
       <c r="AS12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT12">
         <v>8.4</v>
@@ -3525,7 +3525,7 @@
         <v>10</v>
       </c>
       <c r="AW12">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3537,25 +3537,25 @@
         <v>14</v>
       </c>
       <c r="BA12">
+        <v>7.4</v>
+      </c>
+      <c r="BB12">
+        <v>7</v>
+      </c>
+      <c r="BC12">
+        <v>13</v>
+      </c>
+      <c r="BD12">
         <v>7.2</v>
       </c>
-      <c r="BB12">
+      <c r="BE12">
+        <v>8</v>
+      </c>
+      <c r="BF12">
         <v>6.8</v>
       </c>
-      <c r="BC12">
-        <v>6.6</v>
-      </c>
-      <c r="BD12">
+      <c r="BG12">
         <v>7</v>
-      </c>
-      <c r="BE12">
-        <v>7.8</v>
-      </c>
-      <c r="BF12">
-        <v>6.6</v>
-      </c>
-      <c r="BG12">
-        <v>6.8</v>
       </c>
       <c r="BH12">
         <v>3.25</v>
@@ -3638,7 +3638,7 @@
         <v>119</v>
       </c>
       <c r="F13">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G13">
         <v>2.04</v>
@@ -3647,22 +3647,22 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J13">
         <v>3.15</v>
       </c>
       <c r="K13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M13">
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
         <v>1.61</v>
@@ -3677,7 +3677,7 @@
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13">
         <v>2.36</v>
@@ -3692,7 +3692,7 @@
         <v>1.96</v>
       </c>
       <c r="X13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>12</v>
@@ -3701,7 +3701,7 @@
         <v>46</v>
       </c>
       <c r="AA13">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>6.2</v>
@@ -3710,52 +3710,52 @@
         <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AE13">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF13">
         <v>12.5</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
         <v>36</v>
       </c>
       <c r="AI13">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AJ13">
         <v>30</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL13">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM13">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN13">
         <v>34</v>
       </c>
       <c r="AO13">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
         <v>10.5</v>
       </c>
       <c r="AR13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT13">
         <v>5.5</v>
@@ -3764,10 +3764,10 @@
         <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13">
         <v>9</v>
@@ -3776,13 +3776,13 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BA13">
         <v>9</v>
       </c>
       <c r="BB13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC13">
         <v>7.2</v>
@@ -3791,13 +3791,13 @@
         <v>8.6</v>
       </c>
       <c r="BE13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13">
         <v>20</v>
       </c>
       <c r="BG13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH13">
         <v>2.6</v>
@@ -3839,7 +3839,7 @@
         <v>8.4</v>
       </c>
       <c r="BU13">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3889,7 +3889,7 @@
         <v>12.5</v>
       </c>
       <c r="I14">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="J14">
         <v>5.5</v>
@@ -3904,7 +3904,7 @@
         <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
         <v>1.35</v>
@@ -3913,16 +3913,16 @@
         <v>1.86</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S14">
         <v>3.7</v>
       </c>
       <c r="T14">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U14">
         <v>1.56</v>
@@ -3955,31 +3955,31 @@
         <v>60</v>
       </c>
       <c r="AE14">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AF14">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AG14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AI14">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AJ14">
         <v>9.800000000000001</v>
       </c>
       <c r="AK14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL14">
         <v>80</v>
       </c>
       <c r="AM14">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AN14">
         <v>7.4</v>
@@ -3991,13 +3991,13 @@
         <v>13</v>
       </c>
       <c r="AQ14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR14">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AS14">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT14">
         <v>5.7</v>
@@ -4006,10 +4006,10 @@
         <v>12</v>
       </c>
       <c r="AV14">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AX14">
         <v>5.8</v>
@@ -4018,49 +4018,49 @@
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA14">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BB14">
         <v>8.4</v>
       </c>
       <c r="BC14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD14">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE14">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BF14">
         <v>5.6</v>
       </c>
       <c r="BG14">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
         <v>3.4</v>
       </c>
       <c r="BI14">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14">
         <v>15.5</v>
       </c>
       <c r="BK14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BN14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BO14">
         <v>3.05</v>
@@ -4075,31 +4075,31 @@
         <v>34</v>
       </c>
       <c r="BS14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT14">
         <v>17</v>
       </c>
       <c r="BU14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BZ14">
         <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="s">
         <v>122</v>
@@ -4125,7 +4125,7 @@
         <v>2.18</v>
       </c>
       <c r="G15">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
         <v>3.25</v>
@@ -4140,13 +4140,13 @@
         <v>3.75</v>
       </c>
       <c r="L15">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O15">
         <v>1.36</v>
@@ -4185,7 +4185,7 @@
         <v>34</v>
       </c>
       <c r="AA15">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB15">
         <v>9.4</v>
@@ -4209,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="AI15">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
         <v>42</v>
@@ -4218,10 +4218,10 @@
         <v>38</v>
       </c>
       <c r="AL15">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM15">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN15">
         <v>23</v>
@@ -4284,22 +4284,22 @@
         <v>7.6</v>
       </c>
       <c r="BH15">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BI15">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BJ15">
         <v>11.5</v>
       </c>
       <c r="BK15">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN15">
         <v>5.7</v>
@@ -4311,13 +4311,13 @@
         <v>20</v>
       </c>
       <c r="BQ15">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BR15">
         <v>38</v>
       </c>
       <c r="BS15">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BT15">
         <v>7.8</v>
@@ -4329,19 +4329,19 @@
         <v>36</v>
       </c>
       <c r="BW15">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BX15">
         <v>55</v>
       </c>
       <c r="BY15">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ15">
         <v>36</v>
       </c>
       <c r="CA15">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="CB15" t="s">
         <v>122</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-12.xlsx
@@ -382,7 +382,7 @@
     <t>CSD Rangers</t>
   </si>
   <si>
-    <t>2026-08-11 20:28:29</t>
+    <t>2026-08-11 22:37:23</t>
   </si>
 </sst>
 </file>
@@ -976,226 +976,226 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>2.46</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>44</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>1.26</v>
       </c>
       <c r="I2">
+        <v>1.27</v>
+      </c>
+      <c r="J2">
+        <v>5.4</v>
+      </c>
+      <c r="K2">
+        <v>5.6</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.64</v>
+      </c>
+      <c r="O2">
+        <v>2.52</v>
+      </c>
+      <c r="P2">
+        <v>1.08</v>
+      </c>
+      <c r="Q2">
+        <v>12</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>75</v>
+      </c>
+      <c r="T2">
         <v>3.8</v>
       </c>
-      <c r="J2">
-        <v>2.98</v>
-      </c>
-      <c r="K2">
-        <v>3.05</v>
-      </c>
-      <c r="L2">
-        <v>1.69</v>
-      </c>
-      <c r="M2">
-        <v>1.15</v>
-      </c>
-      <c r="N2">
-        <v>2.48</v>
-      </c>
-      <c r="O2">
-        <v>1.64</v>
-      </c>
-      <c r="P2">
-        <v>1.47</v>
-      </c>
-      <c r="Q2">
-        <v>3</v>
-      </c>
-      <c r="R2">
-        <v>1.16</v>
-      </c>
-      <c r="S2">
-        <v>6.6</v>
-      </c>
-      <c r="T2">
-        <v>2.32</v>
-      </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
         <v>1.66</v>
       </c>
-      <c r="X2">
-        <v>7.6</v>
-      </c>
-      <c r="Y2">
-        <v>9.6</v>
-      </c>
       <c r="Z2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>6.8</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>6.2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.62</v>
+      </c>
+      <c r="AR2">
         <v>7</v>
       </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
-      <c r="AD2">
-        <v>17.5</v>
-      </c>
-      <c r="AE2">
-        <v>65</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>950</v>
-      </c>
-      <c r="AJ2">
-        <v>38</v>
-      </c>
-      <c r="AK2">
-        <v>40</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>44</v>
-      </c>
-      <c r="AO2">
-        <v>110</v>
-      </c>
-      <c r="AP2">
-        <v>6.8</v>
-      </c>
-      <c r="AQ2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
       <c r="AS2">
-        <v>70</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="BA2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="BB2">
+        <v>6.4</v>
+      </c>
+      <c r="BC2">
+        <v>70</v>
+      </c>
+      <c r="BD2">
+        <v>46</v>
+      </c>
+      <c r="BE2">
+        <v>46</v>
+      </c>
+      <c r="BF2">
+        <v>46</v>
+      </c>
+      <c r="BG2">
         <v>32</v>
       </c>
-      <c r="BC2">
-        <v>36</v>
-      </c>
-      <c r="BD2">
-        <v>65</v>
-      </c>
-      <c r="BE2">
-        <v>160</v>
-      </c>
-      <c r="BF2">
-        <v>36</v>
-      </c>
-      <c r="BG2">
-        <v>70</v>
-      </c>
       <c r="BH2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>122</v>
@@ -1218,226 +1218,226 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="G3">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="I3">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
+        <v>8</v>
+      </c>
+      <c r="T3">
+        <v>2.92</v>
+      </c>
+      <c r="U3">
+        <v>1.45</v>
+      </c>
+      <c r="V3">
+        <v>1.02</v>
+      </c>
+      <c r="W3">
         <v>5.7</v>
       </c>
-      <c r="T3">
-        <v>2.46</v>
-      </c>
-      <c r="U3">
-        <v>1.63</v>
-      </c>
-      <c r="V3">
-        <v>1.18</v>
-      </c>
-      <c r="W3">
-        <v>2.28</v>
-      </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>3.5</v>
+      </c>
+      <c r="AC3">
         <v>8.800000000000001</v>
       </c>
-      <c r="Y3">
-        <v>14.5</v>
-      </c>
-      <c r="Z3">
-        <v>48</v>
-      </c>
-      <c r="AA3">
-        <v>240</v>
-      </c>
-      <c r="AB3">
-        <v>5.7</v>
-      </c>
-      <c r="AC3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD3">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AE3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>65</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
         <v>10.5</v>
       </c>
-      <c r="AH3">
-        <v>32</v>
-      </c>
-      <c r="AI3">
-        <v>200</v>
-      </c>
-      <c r="AJ3">
-        <v>18.5</v>
-      </c>
       <c r="AK3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AM3">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO3">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR3">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3">
+        <v>44</v>
+      </c>
+      <c r="AW3">
+        <v>260</v>
+      </c>
+      <c r="AX3">
+        <v>3.85</v>
+      </c>
+      <c r="AY3">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3">
+        <v>44</v>
+      </c>
+      <c r="BA3">
+        <v>330</v>
+      </c>
+      <c r="BB3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3">
         <v>23</v>
       </c>
-      <c r="AW3">
-        <v>34</v>
-      </c>
-      <c r="AX3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>29</v>
-      </c>
-      <c r="BA3">
-        <v>34</v>
-      </c>
-      <c r="BB3">
-        <v>17.5</v>
-      </c>
-      <c r="BC3">
-        <v>22</v>
-      </c>
       <c r="BD3">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="BE3">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>440</v>
       </c>
       <c r="BH3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>122</v>
@@ -1472,7 +1472,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1484,13 +1484,13 @@
         <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O4">
         <v>1.3</v>
       </c>
       <c r="P4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q4">
         <v>1.62</v>
@@ -1735,7 +1735,7 @@
         <v>1.49</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R5">
         <v>1.16</v>
@@ -1807,7 +1807,7 @@
         <v>180</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AP5">
         <v>6.2</v>
@@ -1819,7 +1819,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
         <v>6.8</v>
@@ -1843,10 +1843,10 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC5">
         <v>6.2</v>
@@ -1855,10 +1855,10 @@
         <v>6.4</v>
       </c>
       <c r="BE5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5">
         <v>9</v>
@@ -1956,7 +1956,7 @@
         <v>5.9</v>
       </c>
       <c r="J6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
         <v>3.45</v>
@@ -1986,7 +1986,7 @@
         <v>5.3</v>
       </c>
       <c r="T6">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
         <v>1.67</v>
@@ -2001,7 +2001,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z6">
         <v>48</v>
@@ -2013,10 +2013,10 @@
         <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6">
         <v>130</v>
@@ -2028,7 +2028,7 @@
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI6">
         <v>540</v>
@@ -2037,7 +2037,7 @@
         <v>28</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL6">
         <v>75</v>
@@ -2046,7 +2046,7 @@
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO6">
         <v>700</v>
@@ -2058,10 +2058,10 @@
         <v>10</v>
       </c>
       <c r="AR6">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
         <v>5.4</v>
@@ -2073,7 +2073,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
         <v>8.800000000000001</v>
@@ -2085,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="BA6">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
         <v>18</v>
@@ -2094,16 +2094,16 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF6">
         <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2186,7 +2186,7 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -2198,13 +2198,13 @@
         <v>3.45</v>
       </c>
       <c r="J7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K7">
         <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M7">
         <v>1.14</v>
@@ -2255,7 +2255,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD7">
         <v>16</v>
@@ -2303,7 +2303,7 @@
         <v>17</v>
       </c>
       <c r="AS7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
         <v>6.6</v>
@@ -2315,7 +2315,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2327,25 +2327,25 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
+        <v>8.6</v>
+      </c>
+      <c r="BB7">
+        <v>8</v>
+      </c>
+      <c r="BC7">
+        <v>7.8</v>
+      </c>
+      <c r="BD7">
         <v>8.4</v>
       </c>
-      <c r="BB7">
-        <v>7.8</v>
-      </c>
-      <c r="BC7">
-        <v>7.6</v>
-      </c>
-      <c r="BD7">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF7">
         <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>2.64</v>
@@ -2431,7 +2431,7 @@
         <v>7.2</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="H8">
         <v>1.56</v>
@@ -2467,7 +2467,7 @@
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T8">
         <v>2.24</v>
@@ -2479,10 +2479,10 @@
         <v>2.54</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8">
         <v>6.6</v>
@@ -2560,7 +2560,7 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY8">
         <v>26</v>
@@ -2569,19 +2569,19 @@
         <v>6.2</v>
       </c>
       <c r="BA8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB8">
         <v>7.4</v>
       </c>
       <c r="BC8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF8">
         <v>7.4</v>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="W9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3181,13 +3181,13 @@
         <v>1.26</v>
       </c>
       <c r="O11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
         <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R11">
         <v>1.12</v>
@@ -3396,13 +3396,13 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G12">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H12">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
         <v>3.2</v>
@@ -3411,7 +3411,7 @@
         <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L12">
         <v>1.44</v>
@@ -3423,10 +3423,10 @@
         <v>3.25</v>
       </c>
       <c r="O12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q12">
         <v>2.08</v>
@@ -3438,19 +3438,19 @@
         <v>3.85</v>
       </c>
       <c r="T12">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U12">
         <v>2.1</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y12">
         <v>11.5</v>
@@ -3504,25 +3504,25 @@
         <v>38</v>
       </c>
       <c r="AP12">
+        <v>10</v>
+      </c>
+      <c r="AQ12">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AQ12">
-        <v>8.4</v>
       </c>
       <c r="AR12">
         <v>17</v>
       </c>
       <c r="AS12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW12">
         <v>14.5</v>
@@ -3531,31 +3531,31 @@
         <v>14.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12">
+        <v>7.8</v>
+      </c>
+      <c r="BB12">
         <v>7.4</v>
-      </c>
-      <c r="BB12">
-        <v>7</v>
       </c>
       <c r="BC12">
         <v>13</v>
       </c>
       <c r="BD12">
+        <v>38</v>
+      </c>
+      <c r="BE12">
+        <v>8.4</v>
+      </c>
+      <c r="BF12">
+        <v>7</v>
+      </c>
+      <c r="BG12">
         <v>7.2</v>
-      </c>
-      <c r="BE12">
-        <v>8</v>
-      </c>
-      <c r="BF12">
-        <v>6.8</v>
-      </c>
-      <c r="BG12">
-        <v>7</v>
       </c>
       <c r="BH12">
         <v>3.25</v>
@@ -3644,7 +3644,7 @@
         <v>2.04</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I13">
         <v>5.5</v>
@@ -3653,22 +3653,22 @@
         <v>3.15</v>
       </c>
       <c r="K13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M13">
         <v>1.14</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
         <v>1.61</v>
       </c>
       <c r="P13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3677,7 +3677,7 @@
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>2.36</v>
@@ -3692,7 +3692,7 @@
         <v>1.96</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13">
         <v>12</v>
@@ -3710,7 +3710,7 @@
         <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE13">
         <v>700</v>
@@ -3755,19 +3755,19 @@
         <v>7.6</v>
       </c>
       <c r="AS13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT13">
         <v>5.5</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV13">
         <v>16.5</v>
       </c>
       <c r="AW13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX13">
         <v>9</v>
@@ -3776,88 +3776,88 @@
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
         <v>20</v>
       </c>
       <c r="BG13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI13">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="BN13">
         <v>4.3</v>
       </c>
       <c r="BO13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
+        <v>13</v>
+      </c>
+      <c r="BT13">
+        <v>8.6</v>
+      </c>
+      <c r="BU13">
+        <v>5.9</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>14</v>
       </c>
-      <c r="BT13">
-        <v>8.4</v>
-      </c>
-      <c r="BU13">
-        <v>6</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>2.22</v>
-      </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB13" t="s">
         <v>122</v>
@@ -3880,22 +3880,22 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="G14">
         <v>1.35</v>
       </c>
       <c r="H14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I14">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="J14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L14">
         <v>1.41</v>
@@ -3907,10 +3907,10 @@
         <v>3.55</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q14">
         <v>2.04</v>
@@ -3922,40 +3922,40 @@
         <v>3.7</v>
       </c>
       <c r="T14">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="U14">
         <v>1.56</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X14">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z14">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AB14">
         <v>6.4</v>
       </c>
       <c r="AC14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD14">
         <v>60</v>
       </c>
       <c r="AE14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AF14">
         <v>6.6</v>
@@ -3964,64 +3964,64 @@
         <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AI14">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AJ14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK14">
         <v>18</v>
       </c>
       <c r="AL14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM14">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="AN14">
         <v>7.4</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="AP14">
         <v>13</v>
       </c>
       <c r="AQ14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AR14">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AS14">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AW14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX14">
         <v>5.8</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BA14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB14">
         <v>8.4</v>
@@ -4030,16 +4030,16 @@
         <v>15.5</v>
       </c>
       <c r="BD14">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF14">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG14">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH14">
         <v>3.4</v>
@@ -4149,10 +4149,10 @@
         <v>3.15</v>
       </c>
       <c r="O15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4209,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="AI15">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ15">
         <v>42</v>
@@ -4236,19 +4236,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS15">
         <v>7.8</v>
       </c>
       <c r="AT15">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU15">
         <v>6.6</v>
       </c>
       <c r="AV15">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW15">
         <v>7.4</v>
@@ -4257,10 +4257,10 @@
         <v>11</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA15">
         <v>7.6</v>
@@ -4269,16 +4269,16 @@
         <v>6.8</v>
       </c>
       <c r="BC15">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BE15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG15">
         <v>7.6</v>
